--- a/TT_apr26.xlsx
+++ b/TT_apr26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ittea\.gemini\antigravity\scratch\substitution26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6EB2031-5E60-4FF8-B321-9B5CF50B3F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078EACC5-5F6E-48E5-9FC3-25764667275E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87749542-9008-4FB2-99EF-E6484056E6E3}"/>
   </bookViews>
@@ -12894,10 +12894,9 @@
       <c r="D337" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="E337" s="14" t="s">
+      <c r="F337" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F337" s="14"/>
       <c r="G337" s="14" t="s">
         <v>329</v>
       </c>

--- a/TT_apr26.xlsx
+++ b/TT_apr26.xlsx
@@ -1,40 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ittea\.gemini\antigravity\scratch\substitution26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{078EACC5-5F6E-48E5-9FC3-25764667275E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACF4FE7-1508-4338-98C8-F0F4A0780318}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87749542-9008-4FB2-99EF-E6484056E6E3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{87749542-9008-4FB2-99EF-E6484056E6E3}"/>
   </bookViews>
   <sheets>
     <sheet name="TT_Apr26" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TT_Apr26!$A$1:$L$535</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4407" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4409" uniqueCount="536">
   <si>
     <t>tname</t>
   </si>
@@ -1302,12 +1296,6 @@
     <t>5B</t>
   </si>
   <si>
-    <t>SUPW4</t>
-  </si>
-  <si>
-    <t>SUPW5</t>
-  </si>
-  <si>
     <t>ADITI SABARWAL</t>
   </si>
   <si>
@@ -1645,6 +1633,9 @@
   </si>
   <si>
     <t>7A-LIB</t>
+  </si>
+  <si>
+    <t>CT 3B</t>
   </si>
 </sst>
 </file>
@@ -1905,7 +1896,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1959,6 +1950,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2274,22 +2268,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF073B80-F741-476C-ABC5-43118BEB6522}">
   <dimension ref="A1:L535"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" customWidth="1"/>
-    <col min="11" max="12" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="6" max="6" width="15.88671875" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="12.109375" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" customWidth="1"/>
+    <col min="11" max="12" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2327,7 +2321,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -2349,7 +2343,7 @@
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>12</v>
       </c>
@@ -2373,7 +2367,7 @@
       <c r="K3" s="6"/>
       <c r="L3" s="11"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
@@ -2393,7 +2387,7 @@
       <c r="K4" s="6"/>
       <c r="L4" s="11"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>12</v>
       </c>
@@ -2415,7 +2409,7 @@
       <c r="K5" s="6"/>
       <c r="L5" s="11"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
@@ -2435,7 +2429,7 @@
       <c r="K6" s="6"/>
       <c r="L6" s="11"/>
     </row>
-    <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>12</v>
       </c>
@@ -2457,7 +2451,7 @@
       <c r="K7" s="14"/>
       <c r="L7" s="15"/>
     </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>30</v>
       </c>
@@ -2481,7 +2475,7 @@
       <c r="K8" s="7"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>30</v>
       </c>
@@ -2505,7 +2499,7 @@
       <c r="K9" s="6"/>
       <c r="L9" s="11"/>
     </row>
-    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>30</v>
       </c>
@@ -2529,7 +2523,7 @@
       <c r="K10" s="6"/>
       <c r="L10" s="11"/>
     </row>
-    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>30</v>
       </c>
@@ -2551,7 +2545,7 @@
       <c r="K11" s="6"/>
       <c r="L11" s="11"/>
     </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>30</v>
       </c>
@@ -2575,7 +2569,7 @@
       <c r="K12" s="6"/>
       <c r="L12" s="11"/>
     </row>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>30</v>
       </c>
@@ -2597,7 +2591,7 @@
       <c r="K13" s="14"/>
       <c r="L13" s="15"/>
     </row>
-    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>42</v>
       </c>
@@ -2629,7 +2623,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>42</v>
       </c>
@@ -2659,7 +2653,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>42</v>
       </c>
@@ -2689,7 +2683,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>42</v>
       </c>
@@ -2717,7 +2711,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="12" t="s">
         <v>42</v>
       </c>
@@ -2749,7 +2743,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>42</v>
       </c>
@@ -2783,7 +2777,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="12" t="s">
         <v>49</v>
       </c>
@@ -2817,7 +2811,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="12" t="s">
         <v>49</v>
       </c>
@@ -2851,7 +2845,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="12" t="s">
         <v>49</v>
       </c>
@@ -2885,7 +2879,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="12" t="s">
         <v>49</v>
       </c>
@@ -2919,7 +2913,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>49</v>
       </c>
@@ -2951,7 +2945,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="12" t="s">
         <v>49</v>
       </c>
@@ -2981,7 +2975,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="12" t="s">
         <v>56</v>
       </c>
@@ -3009,7 +3003,7 @@
       </c>
       <c r="L26" s="8"/>
     </row>
-    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="12" t="s">
         <v>56</v>
       </c>
@@ -3035,7 +3029,7 @@
       <c r="K27" s="6"/>
       <c r="L27" s="11"/>
     </row>
-    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="12" t="s">
         <v>56</v>
       </c>
@@ -3065,7 +3059,7 @@
       <c r="K28" s="6"/>
       <c r="L28" s="11"/>
     </row>
-    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="12" t="s">
         <v>56</v>
       </c>
@@ -3091,7 +3085,7 @@
       <c r="K29" s="6"/>
       <c r="L29" s="11"/>
     </row>
-    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12" t="s">
         <v>56</v>
       </c>
@@ -3119,7 +3113,7 @@
       <c r="K30" s="6"/>
       <c r="L30" s="11"/>
     </row>
-    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="12" t="s">
         <v>56</v>
       </c>
@@ -3147,7 +3141,7 @@
       <c r="K31" s="14"/>
       <c r="L31" s="15"/>
     </row>
-    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="12" t="s">
         <v>62</v>
       </c>
@@ -3177,7 +3171,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="12" t="s">
         <v>62</v>
       </c>
@@ -3207,7 +3201,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
         <v>62</v>
       </c>
@@ -3241,7 +3235,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="12" t="s">
         <v>62</v>
       </c>
@@ -3271,7 +3265,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="12" t="s">
         <v>62</v>
       </c>
@@ -3301,7 +3295,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="12" t="s">
         <v>62</v>
       </c>
@@ -3335,7 +3329,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="12" t="s">
         <v>68</v>
       </c>
@@ -3348,8 +3342,7 @@
       <c r="D38" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7" t="s">
+      <c r="E38" s="7" t="s">
         <v>71</v>
       </c>
       <c r="G38" s="7" t="s">
@@ -3369,7 +3362,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="12" t="s">
         <v>68</v>
       </c>
@@ -3403,7 +3396,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="12" t="s">
         <v>68</v>
       </c>
@@ -3437,7 +3430,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
         <v>68</v>
       </c>
@@ -3471,7 +3464,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="12" t="s">
         <v>68</v>
       </c>
@@ -3503,7 +3496,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="12" t="s">
         <v>68</v>
       </c>
@@ -3537,7 +3530,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="12" t="s">
         <v>76</v>
       </c>
@@ -3569,7 +3562,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="12" t="s">
         <v>76</v>
       </c>
@@ -3603,7 +3596,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="12" t="s">
         <v>76</v>
       </c>
@@ -3637,7 +3630,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="12" t="s">
         <v>76</v>
       </c>
@@ -3671,7 +3664,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="12" t="s">
         <v>76</v>
       </c>
@@ -3705,7 +3698,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="12" t="s">
         <v>76</v>
       </c>
@@ -3739,7 +3732,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="12" t="s">
         <v>83</v>
       </c>
@@ -3771,7 +3764,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="12" t="s">
         <v>83</v>
       </c>
@@ -3803,7 +3796,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="12" t="s">
         <v>83</v>
       </c>
@@ -3835,7 +3828,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="12" t="s">
         <v>83</v>
       </c>
@@ -3867,7 +3860,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="12" t="s">
         <v>83</v>
       </c>
@@ -3899,7 +3892,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="12" t="s">
         <v>83</v>
       </c>
@@ -3931,7 +3924,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="12" t="s">
         <v>94</v>
       </c>
@@ -3965,7 +3958,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="12" t="s">
         <v>94</v>
       </c>
@@ -3999,7 +3992,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="12" t="s">
         <v>94</v>
       </c>
@@ -4031,7 +4024,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="12" t="s">
         <v>94</v>
       </c>
@@ -4061,7 +4054,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="12" t="s">
         <v>94</v>
       </c>
@@ -4093,7 +4086,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="12" t="s">
         <v>94</v>
       </c>
@@ -4125,7 +4118,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="12" t="s">
         <v>103</v>
       </c>
@@ -4155,7 +4148,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="12" t="s">
         <v>103</v>
       </c>
@@ -4189,7 +4182,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="12" t="s">
         <v>103</v>
       </c>
@@ -4219,7 +4212,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="12" t="s">
         <v>103</v>
       </c>
@@ -4251,7 +4244,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="12" t="s">
         <v>103</v>
       </c>
@@ -4283,7 +4276,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="12" t="s">
         <v>103</v>
       </c>
@@ -4315,7 +4308,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
         <v>110</v>
       </c>
@@ -4347,7 +4340,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="9" t="s">
         <v>110</v>
       </c>
@@ -4379,7 +4372,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="s">
         <v>110</v>
       </c>
@@ -4411,7 +4404,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="s">
         <v>110</v>
       </c>
@@ -4443,7 +4436,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="9" t="s">
         <v>110</v>
       </c>
@@ -4475,7 +4468,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="9" t="s">
         <v>110</v>
       </c>
@@ -4505,7 +4498,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="12" t="s">
         <v>116</v>
       </c>
@@ -4539,7 +4532,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="12" t="s">
         <v>116</v>
       </c>
@@ -4573,7 +4566,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="12" t="s">
         <v>116</v>
       </c>
@@ -4607,7 +4600,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="12" t="s">
         <v>116</v>
       </c>
@@ -4641,7 +4634,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="12" t="s">
         <v>116</v>
       </c>
@@ -4673,7 +4666,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="12" t="s">
         <v>116</v>
       </c>
@@ -4707,7 +4700,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="12" t="s">
         <v>123</v>
       </c>
@@ -4739,7 +4732,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="12" t="s">
         <v>123</v>
       </c>
@@ -4769,7 +4762,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="12" t="s">
         <v>123</v>
       </c>
@@ -4799,7 +4792,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="12" t="s">
         <v>123</v>
       </c>
@@ -4831,7 +4824,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="12" t="s">
         <v>123</v>
       </c>
@@ -4863,7 +4856,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="12" t="s">
         <v>123</v>
       </c>
@@ -4895,7 +4888,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="12" t="s">
         <v>129</v>
       </c>
@@ -4929,7 +4922,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="12" t="s">
         <v>129</v>
       </c>
@@ -4963,7 +4956,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="12" t="s">
         <v>129</v>
       </c>
@@ -4997,7 +4990,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="12" t="s">
         <v>129</v>
       </c>
@@ -5029,7 +5022,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="12" t="s">
         <v>129</v>
       </c>
@@ -5061,7 +5054,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="12" t="s">
         <v>129</v>
       </c>
@@ -5093,7 +5086,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="12" t="s">
         <v>134</v>
       </c>
@@ -5125,7 +5118,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="12" t="s">
         <v>134</v>
       </c>
@@ -5157,7 +5150,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="12" t="s">
         <v>134</v>
       </c>
@@ -5189,7 +5182,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="12" t="s">
         <v>134</v>
       </c>
@@ -5223,7 +5216,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="12" t="s">
         <v>134</v>
       </c>
@@ -5257,7 +5250,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="12" t="s">
         <v>134</v>
       </c>
@@ -5289,7 +5282,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="9" t="s">
         <v>138</v>
       </c>
@@ -5323,7 +5316,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="9" t="s">
         <v>138</v>
       </c>
@@ -5355,7 +5348,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="9" t="s">
         <v>138</v>
       </c>
@@ -5387,7 +5380,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="9" t="s">
         <v>138</v>
       </c>
@@ -5421,7 +5414,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="9" t="s">
         <v>138</v>
       </c>
@@ -5451,7 +5444,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="9" t="s">
         <v>138</v>
       </c>
@@ -5483,7 +5476,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="12" t="s">
         <v>141</v>
       </c>
@@ -5515,7 +5508,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="12" t="s">
         <v>141</v>
       </c>
@@ -5547,7 +5540,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="12" t="s">
         <v>141</v>
       </c>
@@ -5581,7 +5574,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="12" t="s">
         <v>141</v>
       </c>
@@ -5615,7 +5608,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="12" t="s">
         <v>141</v>
       </c>
@@ -5645,7 +5638,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="12" t="s">
         <v>141</v>
       </c>
@@ -5679,7 +5672,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="12" t="s">
         <v>145</v>
       </c>
@@ -5713,7 +5706,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="12" t="s">
         <v>145</v>
       </c>
@@ -5745,7 +5738,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="12" t="s">
         <v>145</v>
       </c>
@@ -5779,7 +5772,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="12" t="s">
         <v>145</v>
       </c>
@@ -5811,7 +5804,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="12" t="s">
         <v>145</v>
       </c>
@@ -5841,7 +5834,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="12" t="s">
         <v>145</v>
       </c>
@@ -5875,7 +5868,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="12" t="s">
         <v>149</v>
       </c>
@@ -5907,7 +5900,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="12" t="s">
         <v>149</v>
       </c>
@@ -5941,7 +5934,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="12" t="s">
         <v>149</v>
       </c>
@@ -5973,7 +5966,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="12" t="s">
         <v>149</v>
       </c>
@@ -6003,7 +5996,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="12" t="s">
         <v>149</v>
       </c>
@@ -6037,7 +6030,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="12" t="s">
         <v>149</v>
       </c>
@@ -6071,7 +6064,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="12" t="s">
         <v>153</v>
       </c>
@@ -6103,7 +6096,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="12" t="s">
         <v>153</v>
       </c>
@@ -6137,7 +6130,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="12" t="s">
         <v>153</v>
       </c>
@@ -6169,7 +6162,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="12" t="s">
         <v>153</v>
       </c>
@@ -6199,7 +6192,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="12" t="s">
         <v>153</v>
       </c>
@@ -6233,7 +6226,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="12" t="s">
         <v>153</v>
       </c>
@@ -6267,7 +6260,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="12" t="s">
         <v>161</v>
       </c>
@@ -6299,7 +6292,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="12" t="s">
         <v>161</v>
       </c>
@@ -6333,7 +6326,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="12" t="s">
         <v>161</v>
       </c>
@@ -6367,7 +6360,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="12" t="s">
         <v>161</v>
       </c>
@@ -6399,7 +6392,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="12" t="s">
         <v>161</v>
       </c>
@@ -6429,7 +6422,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="12" t="s">
         <v>161</v>
       </c>
@@ -6461,7 +6454,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="12" t="s">
         <v>167</v>
       </c>
@@ -6495,7 +6488,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="12" t="s">
         <v>167</v>
       </c>
@@ -6525,7 +6518,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="12" t="s">
         <v>167</v>
       </c>
@@ -6559,7 +6552,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="12" t="s">
         <v>167</v>
       </c>
@@ -6593,7 +6586,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="12" t="s">
         <v>167</v>
       </c>
@@ -6627,7 +6620,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="12" t="s">
         <v>167</v>
       </c>
@@ -6659,7 +6652,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>175</v>
       </c>
@@ -6689,7 +6682,7 @@
       </c>
       <c r="L140" s="8"/>
     </row>
-    <row r="141" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>175</v>
       </c>
@@ -6717,7 +6710,7 @@
       </c>
       <c r="L141" s="11"/>
     </row>
-    <row r="142" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
         <v>175</v>
       </c>
@@ -6747,7 +6740,7 @@
       </c>
       <c r="L142" s="11"/>
     </row>
-    <row r="143" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>175</v>
       </c>
@@ -6777,7 +6770,7 @@
       </c>
       <c r="L143" s="11"/>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>175</v>
       </c>
@@ -6807,7 +6800,7 @@
       </c>
       <c r="L144" s="11"/>
     </row>
-    <row r="145" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="12" t="s">
         <v>175</v>
       </c>
@@ -6837,7 +6830,7 @@
       </c>
       <c r="L145" s="15"/>
     </row>
-    <row r="146" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="12" t="s">
         <v>182</v>
       </c>
@@ -6871,7 +6864,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="12" t="s">
         <v>182</v>
       </c>
@@ -6903,7 +6896,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="12" t="s">
         <v>182</v>
       </c>
@@ -6937,7 +6930,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="12" t="s">
         <v>182</v>
       </c>
@@ -6971,7 +6964,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="12" t="s">
         <v>182</v>
       </c>
@@ -7003,7 +6996,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="12" t="s">
         <v>182</v>
       </c>
@@ -7035,7 +7028,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="12" t="s">
         <v>188</v>
       </c>
@@ -7063,7 +7056,7 @@
       </c>
       <c r="L152" s="8"/>
     </row>
-    <row r="153" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="12" t="s">
         <v>188</v>
       </c>
@@ -7089,7 +7082,7 @@
       <c r="K153" s="6"/>
       <c r="L153" s="11"/>
     </row>
-    <row r="154" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="12" t="s">
         <v>188</v>
       </c>
@@ -7115,7 +7108,7 @@
       </c>
       <c r="L154" s="11"/>
     </row>
-    <row r="155" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="12" t="s">
         <v>188</v>
       </c>
@@ -7143,7 +7136,7 @@
       </c>
       <c r="L155" s="11"/>
     </row>
-    <row r="156" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="12" t="s">
         <v>188</v>
       </c>
@@ -7171,7 +7164,7 @@
       </c>
       <c r="L156" s="11"/>
     </row>
-    <row r="157" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="12" t="s">
         <v>188</v>
       </c>
@@ -7197,7 +7190,7 @@
       <c r="K157" s="14"/>
       <c r="L157" s="15"/>
     </row>
-    <row r="158" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="12" t="s">
         <v>192</v>
       </c>
@@ -7231,7 +7224,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="12" t="s">
         <v>192</v>
       </c>
@@ -7265,7 +7258,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="12" t="s">
         <v>192</v>
       </c>
@@ -7297,7 +7290,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="12" t="s">
         <v>192</v>
       </c>
@@ -7329,7 +7322,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="12" t="s">
         <v>192</v>
       </c>
@@ -7363,7 +7356,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="12" t="s">
         <v>192</v>
       </c>
@@ -7393,7 +7386,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="12" t="s">
         <v>196</v>
       </c>
@@ -7406,13 +7399,12 @@
       <c r="D164" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E164" s="7" t="s">
-        <v>71</v>
-      </c>
       <c r="F164" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="G164" s="7"/>
+      <c r="G164" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="H164" s="7" t="s">
         <v>85</v>
       </c>
@@ -7423,7 +7415,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="12" t="s">
         <v>196</v>
       </c>
@@ -7455,7 +7447,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="12" t="s">
         <v>196</v>
       </c>
@@ -7489,7 +7481,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="12" t="s">
         <v>196</v>
       </c>
@@ -7523,7 +7515,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="12" t="s">
         <v>196</v>
       </c>
@@ -7557,7 +7549,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="12" t="s">
         <v>196</v>
       </c>
@@ -7589,7 +7581,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="12" t="s">
         <v>198</v>
       </c>
@@ -7621,7 +7613,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="12" t="s">
         <v>198</v>
       </c>
@@ -7653,7 +7645,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="12" t="s">
         <v>198</v>
       </c>
@@ -7687,7 +7679,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="12" t="s">
         <v>198</v>
       </c>
@@ -7721,7 +7713,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="12" t="s">
         <v>198</v>
       </c>
@@ -7753,7 +7745,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="12" t="s">
         <v>198</v>
       </c>
@@ -7785,7 +7777,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="12" t="s">
         <v>200</v>
       </c>
@@ -7817,7 +7809,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="12" t="s">
         <v>200</v>
       </c>
@@ -7851,7 +7843,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="12" t="s">
         <v>200</v>
       </c>
@@ -7883,7 +7875,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="12" t="s">
         <v>200</v>
       </c>
@@ -7917,7 +7909,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="12" t="s">
         <v>200</v>
       </c>
@@ -7949,7 +7941,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="12" t="s">
         <v>200</v>
       </c>
@@ -7981,7 +7973,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="12" t="s">
         <v>202</v>
       </c>
@@ -8013,7 +8005,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="12" t="s">
         <v>202</v>
       </c>
@@ -8047,7 +8039,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="12" t="s">
         <v>202</v>
       </c>
@@ -8079,7 +8071,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="12" t="s">
         <v>202</v>
       </c>
@@ -8113,7 +8105,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="12" t="s">
         <v>202</v>
       </c>
@@ -8147,7 +8139,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="12" t="s">
         <v>202</v>
       </c>
@@ -8181,7 +8173,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="12" t="s">
         <v>206</v>
       </c>
@@ -8213,7 +8205,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="12" t="s">
         <v>206</v>
       </c>
@@ -8247,7 +8239,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="12" t="s">
         <v>206</v>
       </c>
@@ -8281,7 +8273,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="12" t="s">
         <v>206</v>
       </c>
@@ -8313,7 +8305,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="12" t="s">
         <v>206</v>
       </c>
@@ -8347,7 +8339,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="12" t="s">
         <v>206</v>
       </c>
@@ -8379,7 +8371,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="12" t="s">
         <v>209</v>
       </c>
@@ -8413,7 +8405,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="12" t="s">
         <v>209</v>
       </c>
@@ -8443,7 +8435,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A196" s="12" t="s">
         <v>209</v>
       </c>
@@ -8475,7 +8467,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A197" s="12" t="s">
         <v>209</v>
       </c>
@@ -8509,7 +8501,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A198" s="12" t="s">
         <v>209</v>
       </c>
@@ -8543,7 +8535,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="12" t="s">
         <v>209</v>
       </c>
@@ -8575,7 +8567,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="12" t="s">
         <v>211</v>
       </c>
@@ -8605,7 +8597,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="12" t="s">
         <v>211</v>
       </c>
@@ -8639,7 +8631,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A202" s="12" t="s">
         <v>211</v>
       </c>
@@ -8671,7 +8663,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="12" t="s">
         <v>211</v>
       </c>
@@ -8703,7 +8695,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A204" s="12" t="s">
         <v>211</v>
       </c>
@@ -8737,7 +8729,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="12" t="s">
         <v>211</v>
       </c>
@@ -8771,7 +8763,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="12" t="s">
         <v>213</v>
       </c>
@@ -8801,7 +8793,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="12" t="s">
         <v>213</v>
       </c>
@@ -8835,7 +8827,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="12" t="s">
         <v>213</v>
       </c>
@@ -8869,7 +8861,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="12" t="s">
         <v>213</v>
       </c>
@@ -8901,7 +8893,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="12" t="s">
         <v>213</v>
       </c>
@@ -8935,7 +8927,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="12" t="s">
         <v>213</v>
       </c>
@@ -8967,7 +8959,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="12" t="s">
         <v>215</v>
       </c>
@@ -9001,7 +8993,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="12" t="s">
         <v>215</v>
       </c>
@@ -9037,7 +9029,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="12" t="s">
         <v>215</v>
       </c>
@@ -9069,7 +9061,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="12" t="s">
         <v>215</v>
       </c>
@@ -9103,7 +9095,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="12" t="s">
         <v>215</v>
       </c>
@@ -9135,7 +9127,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="12" t="s">
         <v>215</v>
       </c>
@@ -9167,7 +9159,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="12" t="s">
         <v>221</v>
       </c>
@@ -9201,7 +9193,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="12" t="s">
         <v>221</v>
       </c>
@@ -9237,7 +9229,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="12" t="s">
         <v>221</v>
       </c>
@@ -9271,7 +9263,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="12" t="s">
         <v>221</v>
       </c>
@@ -9305,7 +9297,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="12" t="s">
         <v>221</v>
       </c>
@@ -9335,7 +9327,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="12" t="s">
         <v>221</v>
       </c>
@@ -9367,7 +9359,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="12" t="s">
         <v>227</v>
       </c>
@@ -9401,7 +9393,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="12" t="s">
         <v>227</v>
       </c>
@@ -9435,7 +9427,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="12" t="s">
         <v>227</v>
       </c>
@@ -9467,7 +9459,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="12" t="s">
         <v>227</v>
       </c>
@@ -9501,7 +9493,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="12" t="s">
         <v>227</v>
       </c>
@@ -9533,7 +9525,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="12" t="s">
         <v>227</v>
       </c>
@@ -9567,7 +9559,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="12" t="s">
         <v>232</v>
       </c>
@@ -9601,7 +9593,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="12" t="s">
         <v>232</v>
       </c>
@@ -9635,7 +9627,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="12" t="s">
         <v>232</v>
       </c>
@@ -9669,7 +9661,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="12" t="s">
         <v>232</v>
       </c>
@@ -9703,7 +9695,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="12" t="s">
         <v>232</v>
       </c>
@@ -9735,7 +9727,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="12" t="s">
         <v>232</v>
       </c>
@@ -9767,7 +9759,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="12" t="s">
         <v>237</v>
       </c>
@@ -9799,7 +9791,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="12" t="s">
         <v>237</v>
       </c>
@@ -9833,7 +9825,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="12" t="s">
         <v>237</v>
       </c>
@@ -9863,7 +9855,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="12" t="s">
         <v>237</v>
       </c>
@@ -9897,7 +9889,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="12" t="s">
         <v>237</v>
       </c>
@@ -9931,7 +9923,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A241" s="12" t="s">
         <v>237</v>
       </c>
@@ -9963,7 +9955,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="4" t="s">
         <v>242</v>
       </c>
@@ -9997,7 +9989,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="9" t="s">
         <v>242</v>
       </c>
@@ -10029,7 +10021,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="9" t="s">
         <v>242</v>
       </c>
@@ -10061,7 +10053,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="9" t="s">
         <v>242</v>
       </c>
@@ -10093,7 +10085,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="9" t="s">
         <v>242</v>
       </c>
@@ -10127,7 +10119,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A247" s="12" t="s">
         <v>242</v>
       </c>
@@ -10161,7 +10153,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A248" s="12" t="s">
         <v>250</v>
       </c>
@@ -10189,7 +10181,7 @@
       <c r="K248" s="7"/>
       <c r="L248" s="8"/>
     </row>
-    <row r="249" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A249" s="12" t="s">
         <v>250</v>
       </c>
@@ -10217,7 +10209,7 @@
       <c r="K249" s="6"/>
       <c r="L249" s="11"/>
     </row>
-    <row r="250" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A250" s="12" t="s">
         <v>250</v>
       </c>
@@ -10245,7 +10237,7 @@
       <c r="K250" s="6"/>
       <c r="L250" s="11"/>
     </row>
-    <row r="251" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A251" s="12" t="s">
         <v>250</v>
       </c>
@@ -10273,7 +10265,7 @@
       </c>
       <c r="L251" s="11"/>
     </row>
-    <row r="252" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A252" s="12" t="s">
         <v>250</v>
       </c>
@@ -10301,7 +10293,7 @@
       <c r="K252" s="6"/>
       <c r="L252" s="11"/>
     </row>
-    <row r="253" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A253" s="12" t="s">
         <v>250</v>
       </c>
@@ -10329,7 +10321,7 @@
       </c>
       <c r="L253" s="15"/>
     </row>
-    <row r="254" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" s="12" t="s">
         <v>256</v>
       </c>
@@ -10359,7 +10351,7 @@
       </c>
       <c r="L254" s="8"/>
     </row>
-    <row r="255" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A255" s="12" t="s">
         <v>256</v>
       </c>
@@ -10385,7 +10377,7 @@
       <c r="K255" s="6"/>
       <c r="L255" s="11"/>
     </row>
-    <row r="256" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="12" t="s">
         <v>256</v>
       </c>
@@ -10413,7 +10405,7 @@
       </c>
       <c r="L256" s="11"/>
     </row>
-    <row r="257" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A257" s="12" t="s">
         <v>256</v>
       </c>
@@ -10443,7 +10435,7 @@
       </c>
       <c r="L257" s="11"/>
     </row>
-    <row r="258" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A258" s="12" t="s">
         <v>256</v>
       </c>
@@ -10469,7 +10461,7 @@
       <c r="K258" s="6"/>
       <c r="L258" s="11"/>
     </row>
-    <row r="259" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A259" s="12" t="s">
         <v>256</v>
       </c>
@@ -10495,7 +10487,7 @@
       </c>
       <c r="L259" s="15"/>
     </row>
-    <row r="260" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="12" t="s">
         <v>258</v>
       </c>
@@ -10527,7 +10519,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="261" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" s="12" t="s">
         <v>258</v>
       </c>
@@ -10561,7 +10553,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" s="12" t="s">
         <v>258</v>
       </c>
@@ -10595,7 +10587,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="12" t="s">
         <v>258</v>
       </c>
@@ -10627,7 +10619,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A264" s="12" t="s">
         <v>258</v>
       </c>
@@ -10661,7 +10653,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A265" s="12" t="s">
         <v>258</v>
       </c>
@@ -10693,7 +10685,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="266" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" s="12" t="s">
         <v>262</v>
       </c>
@@ -10721,7 +10713,7 @@
       </c>
       <c r="L266" s="8"/>
     </row>
-    <row r="267" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A267" s="12" t="s">
         <v>262</v>
       </c>
@@ -10751,7 +10743,7 @@
       <c r="K267" s="6"/>
       <c r="L267" s="11"/>
     </row>
-    <row r="268" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A268" s="12" t="s">
         <v>262</v>
       </c>
@@ -10779,7 +10771,7 @@
       <c r="K268" s="6"/>
       <c r="L268" s="11"/>
     </row>
-    <row r="269" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A269" s="12" t="s">
         <v>262</v>
       </c>
@@ -10809,7 +10801,7 @@
       </c>
       <c r="L269" s="11"/>
     </row>
-    <row r="270" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A270" s="12" t="s">
         <v>262</v>
       </c>
@@ -10839,7 +10831,7 @@
       </c>
       <c r="L270" s="11"/>
     </row>
-    <row r="271" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A271" s="12" t="s">
         <v>262</v>
       </c>
@@ -10869,7 +10861,7 @@
       </c>
       <c r="L271" s="15"/>
     </row>
-    <row r="272" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A272" s="12" t="s">
         <v>273</v>
       </c>
@@ -10897,7 +10889,7 @@
       </c>
       <c r="L272" s="8"/>
     </row>
-    <row r="273" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A273" s="12" t="s">
         <v>273</v>
       </c>
@@ -10929,7 +10921,7 @@
       <c r="K273" s="6"/>
       <c r="L273" s="11"/>
     </row>
-    <row r="274" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A274" s="12" t="s">
         <v>273</v>
       </c>
@@ -10959,7 +10951,7 @@
       <c r="K274" s="6"/>
       <c r="L274" s="11"/>
     </row>
-    <row r="275" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A275" s="12" t="s">
         <v>273</v>
       </c>
@@ -10989,7 +10981,7 @@
       <c r="K275" s="6"/>
       <c r="L275" s="11"/>
     </row>
-    <row r="276" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A276" s="12" t="s">
         <v>273</v>
       </c>
@@ -11015,7 +11007,7 @@
       <c r="K276" s="6"/>
       <c r="L276" s="11"/>
     </row>
-    <row r="277" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" s="12" t="s">
         <v>273</v>
       </c>
@@ -11043,7 +11035,7 @@
       <c r="K277" s="14"/>
       <c r="L277" s="15"/>
     </row>
-    <row r="278" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A278" s="12" t="s">
         <v>284</v>
       </c>
@@ -11075,7 +11067,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="279" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A279" s="12" t="s">
         <v>284</v>
       </c>
@@ -11107,7 +11099,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="280" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A280" s="12" t="s">
         <v>284</v>
       </c>
@@ -11139,7 +11131,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A281" s="12" t="s">
         <v>284</v>
       </c>
@@ -11171,7 +11163,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="282" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A282" s="12" t="s">
         <v>284</v>
       </c>
@@ -11205,7 +11197,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="283" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A283" s="12" t="s">
         <v>284</v>
       </c>
@@ -11239,7 +11231,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="284" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A284" s="12" t="s">
         <v>291</v>
       </c>
@@ -11271,7 +11263,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="285" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A285" s="12" t="s">
         <v>291</v>
       </c>
@@ -11305,7 +11297,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A286" s="12" t="s">
         <v>291</v>
       </c>
@@ -11337,7 +11329,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="287" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A287" s="12" t="s">
         <v>291</v>
       </c>
@@ -11371,7 +11363,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A288" s="12" t="s">
         <v>291</v>
       </c>
@@ -11405,7 +11397,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="289" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A289" s="12" t="s">
         <v>291</v>
       </c>
@@ -11439,7 +11431,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="290" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A290" s="12" t="s">
         <v>301</v>
       </c>
@@ -11469,7 +11461,7 @@
       </c>
       <c r="L290" s="8"/>
     </row>
-    <row r="291" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A291" s="12" t="s">
         <v>301</v>
       </c>
@@ -11499,7 +11491,7 @@
       </c>
       <c r="L291" s="11"/>
     </row>
-    <row r="292" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A292" s="12" t="s">
         <v>301</v>
       </c>
@@ -11527,7 +11519,7 @@
       </c>
       <c r="L292" s="11"/>
     </row>
-    <row r="293" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A293" s="12" t="s">
         <v>301</v>
       </c>
@@ -11555,7 +11547,7 @@
       <c r="K293" s="6"/>
       <c r="L293" s="11"/>
     </row>
-    <row r="294" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A294" s="12" t="s">
         <v>301</v>
       </c>
@@ -11585,7 +11577,7 @@
       <c r="K294" s="6"/>
       <c r="L294" s="11"/>
     </row>
-    <row r="295" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A295" s="12" t="s">
         <v>301</v>
       </c>
@@ -11615,7 +11607,7 @@
       </c>
       <c r="L295" s="15"/>
     </row>
-    <row r="296" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A296" s="12" t="s">
         <v>303</v>
       </c>
@@ -11649,7 +11641,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A297" s="12" t="s">
         <v>303</v>
       </c>
@@ -11683,7 +11675,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A298" s="12" t="s">
         <v>303</v>
       </c>
@@ -11717,7 +11709,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="299" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A299" s="12" t="s">
         <v>303</v>
       </c>
@@ -11749,7 +11741,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="300" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A300" s="12" t="s">
         <v>303</v>
       </c>
@@ -11783,7 +11775,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="301" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A301" s="12" t="s">
         <v>303</v>
       </c>
@@ -11817,7 +11809,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="302" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A302" s="12" t="s">
         <v>305</v>
       </c>
@@ -11845,7 +11837,7 @@
       <c r="K302" s="7"/>
       <c r="L302" s="8"/>
     </row>
-    <row r="303" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A303" s="12" t="s">
         <v>305</v>
       </c>
@@ -11875,7 +11867,7 @@
       </c>
       <c r="L303" s="11"/>
     </row>
-    <row r="304" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A304" s="12" t="s">
         <v>305</v>
       </c>
@@ -11905,7 +11897,7 @@
       </c>
       <c r="L304" s="11"/>
     </row>
-    <row r="305" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A305" s="12" t="s">
         <v>305</v>
       </c>
@@ -11935,7 +11927,7 @@
       </c>
       <c r="L305" s="11"/>
     </row>
-    <row r="306" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A306" s="12" t="s">
         <v>305</v>
       </c>
@@ -11965,7 +11957,7 @@
       </c>
       <c r="L306" s="11"/>
     </row>
-    <row r="307" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A307" s="12" t="s">
         <v>305</v>
       </c>
@@ -11995,7 +11987,7 @@
       </c>
       <c r="L307" s="15"/>
     </row>
-    <row r="308" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A308" s="12" t="s">
         <v>306</v>
       </c>
@@ -12029,7 +12021,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="309" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A309" s="12" t="s">
         <v>306</v>
       </c>
@@ -12061,7 +12053,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="310" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A310" s="12" t="s">
         <v>306</v>
       </c>
@@ -12091,7 +12083,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="311" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A311" s="12" t="s">
         <v>306</v>
       </c>
@@ -12121,7 +12113,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="312" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A312" s="12" t="s">
         <v>306</v>
       </c>
@@ -12153,7 +12145,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="313" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A313" s="12" t="s">
         <v>306</v>
       </c>
@@ -12187,7 +12179,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="314" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A314" s="12" t="s">
         <v>308</v>
       </c>
@@ -12219,7 +12211,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="315" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A315" s="12" t="s">
         <v>308</v>
       </c>
@@ -12253,7 +12245,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="316" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A316" s="12" t="s">
         <v>308</v>
       </c>
@@ -12285,7 +12277,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="317" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A317" s="12" t="s">
         <v>308</v>
       </c>
@@ -12317,7 +12309,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="318" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A318" s="12" t="s">
         <v>308</v>
       </c>
@@ -12347,7 +12339,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="319" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A319" s="12" t="s">
         <v>308</v>
       </c>
@@ -12379,7 +12371,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="320" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A320" s="12" t="s">
         <v>310</v>
       </c>
@@ -12407,7 +12399,7 @@
       <c r="K320" s="7"/>
       <c r="L320" s="8"/>
     </row>
-    <row r="321" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A321" s="12" t="s">
         <v>310</v>
       </c>
@@ -12437,7 +12429,7 @@
       </c>
       <c r="L321" s="11"/>
     </row>
-    <row r="322" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A322" s="12" t="s">
         <v>310</v>
       </c>
@@ -12465,7 +12457,7 @@
       </c>
       <c r="L322" s="11"/>
     </row>
-    <row r="323" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A323" s="12" t="s">
         <v>310</v>
       </c>
@@ -12493,7 +12485,7 @@
       <c r="K323" s="6"/>
       <c r="L323" s="11"/>
     </row>
-    <row r="324" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A324" s="12" t="s">
         <v>310</v>
       </c>
@@ -12521,7 +12513,7 @@
       <c r="K324" s="6"/>
       <c r="L324" s="11"/>
     </row>
-    <row r="325" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A325" s="12" t="s">
         <v>310</v>
       </c>
@@ -12549,7 +12541,7 @@
       <c r="K325" s="14"/>
       <c r="L325" s="15"/>
     </row>
-    <row r="326" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A326" s="12" t="s">
         <v>314</v>
       </c>
@@ -12577,7 +12569,7 @@
       </c>
       <c r="L326" s="8"/>
     </row>
-    <row r="327" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A327" s="12" t="s">
         <v>314</v>
       </c>
@@ -12605,7 +12597,7 @@
       <c r="K327" s="6"/>
       <c r="L327" s="11"/>
     </row>
-    <row r="328" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A328" s="12" t="s">
         <v>314</v>
       </c>
@@ -12633,7 +12625,7 @@
       <c r="K328" s="6"/>
       <c r="L328" s="11"/>
     </row>
-    <row r="329" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A329" s="12" t="s">
         <v>314</v>
       </c>
@@ -12661,7 +12653,7 @@
       </c>
       <c r="L329" s="11"/>
     </row>
-    <row r="330" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A330" s="12" t="s">
         <v>314</v>
       </c>
@@ -12689,7 +12681,7 @@
       <c r="K330" s="6"/>
       <c r="L330" s="11"/>
     </row>
-    <row r="331" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A331" s="12" t="s">
         <v>314</v>
       </c>
@@ -12717,7 +12709,7 @@
       </c>
       <c r="L331" s="15"/>
     </row>
-    <row r="332" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A332" s="12" t="s">
         <v>321</v>
       </c>
@@ -12749,7 +12741,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="333" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A333" s="12" t="s">
         <v>321</v>
       </c>
@@ -12783,7 +12775,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="334" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A334" s="12" t="s">
         <v>321</v>
       </c>
@@ -12815,7 +12807,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="335" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A335" s="12" t="s">
         <v>321</v>
       </c>
@@ -12849,7 +12841,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="336" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A336" s="12" t="s">
         <v>321</v>
       </c>
@@ -12881,7 +12873,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="337" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A337" s="12" t="s">
         <v>321</v>
       </c>
@@ -12914,7 +12906,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="338" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A338" s="12" t="s">
         <v>330</v>
       </c>
@@ -12944,7 +12936,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="339" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A339" s="12" t="s">
         <v>330</v>
       </c>
@@ -12976,7 +12968,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="340" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A340" s="12" t="s">
         <v>330</v>
       </c>
@@ -13008,7 +13000,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="341" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A341" s="12" t="s">
         <v>330</v>
       </c>
@@ -13042,7 +13034,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="342" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A342" s="12" t="s">
         <v>330</v>
       </c>
@@ -13076,7 +13068,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="343" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A343" s="12" t="s">
         <v>330</v>
       </c>
@@ -13108,7 +13100,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="344" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A344" s="12" t="s">
         <v>339</v>
       </c>
@@ -13140,7 +13132,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="345" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A345" s="12" t="s">
         <v>339</v>
       </c>
@@ -13172,7 +13164,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="346" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A346" s="12" t="s">
         <v>339</v>
       </c>
@@ -13206,7 +13198,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="347" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A347" s="12" t="s">
         <v>339</v>
       </c>
@@ -13238,7 +13230,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="348" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A348" s="12" t="s">
         <v>339</v>
       </c>
@@ -13270,7 +13262,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="349" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A349" s="12" t="s">
         <v>339</v>
       </c>
@@ -13302,7 +13294,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="350" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A350" s="12" t="s">
         <v>349</v>
       </c>
@@ -13334,7 +13326,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="351" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A351" s="12" t="s">
         <v>349</v>
       </c>
@@ -13366,7 +13358,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="352" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A352" s="12" t="s">
         <v>349</v>
       </c>
@@ -13400,7 +13392,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="353" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A353" s="12" t="s">
         <v>349</v>
       </c>
@@ -13432,7 +13424,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="354" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A354" s="12" t="s">
         <v>349</v>
       </c>
@@ -13466,7 +13458,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="355" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A355" s="12" t="s">
         <v>349</v>
       </c>
@@ -13498,7 +13490,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="356" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A356" s="12" t="s">
         <v>358</v>
       </c>
@@ -13532,7 +13524,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="357" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A357" s="12" t="s">
         <v>358</v>
       </c>
@@ -13564,7 +13556,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="358" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A358" s="12" t="s">
         <v>358</v>
       </c>
@@ -13596,7 +13588,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="359" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A359" s="12" t="s">
         <v>358</v>
       </c>
@@ -13630,7 +13622,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="360" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A360" s="12" t="s">
         <v>358</v>
       </c>
@@ -13664,7 +13656,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="361" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A361" s="12" t="s">
         <v>358</v>
       </c>
@@ -13696,7 +13688,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="362" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A362" s="12" t="s">
         <v>367</v>
       </c>
@@ -13730,7 +13722,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="363" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A363" s="12" t="s">
         <v>367</v>
       </c>
@@ -13760,7 +13752,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="364" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A364" s="12" t="s">
         <v>367</v>
       </c>
@@ -13794,7 +13786,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="365" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A365" s="12" t="s">
         <v>367</v>
       </c>
@@ -13824,7 +13816,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="366" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A366" s="12" t="s">
         <v>367</v>
       </c>
@@ -13858,7 +13850,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="367" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A367" s="12" t="s">
         <v>367</v>
       </c>
@@ -13890,7 +13882,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="368" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A368" s="12" t="s">
         <v>378</v>
       </c>
@@ -13920,7 +13912,7 @@
       </c>
       <c r="L368" s="8"/>
     </row>
-    <row r="369" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A369" s="12" t="s">
         <v>378</v>
       </c>
@@ -13950,7 +13942,7 @@
       </c>
       <c r="L369" s="11"/>
     </row>
-    <row r="370" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A370" s="12" t="s">
         <v>378</v>
       </c>
@@ -13978,7 +13970,7 @@
       </c>
       <c r="L370" s="11"/>
     </row>
-    <row r="371" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A371" s="12" t="s">
         <v>378</v>
       </c>
@@ -14004,7 +13996,7 @@
       <c r="K371" s="6"/>
       <c r="L371" s="11"/>
     </row>
-    <row r="372" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A372" s="12" t="s">
         <v>378</v>
       </c>
@@ -14034,7 +14026,7 @@
       </c>
       <c r="L372" s="11"/>
     </row>
-    <row r="373" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A373" s="12" t="s">
         <v>378</v>
       </c>
@@ -14062,7 +14054,7 @@
       </c>
       <c r="L373" s="15"/>
     </row>
-    <row r="374" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A374" s="12" t="s">
         <v>391</v>
       </c>
@@ -14090,7 +14082,7 @@
       <c r="K374" s="7"/>
       <c r="L374" s="8"/>
     </row>
-    <row r="375" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A375" s="12" t="s">
         <v>391</v>
       </c>
@@ -14118,7 +14110,7 @@
       <c r="K375" s="6"/>
       <c r="L375" s="11"/>
     </row>
-    <row r="376" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A376" s="12" t="s">
         <v>391</v>
       </c>
@@ -14146,7 +14138,7 @@
       <c r="K376" s="6"/>
       <c r="L376" s="11"/>
     </row>
-    <row r="377" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A377" s="12" t="s">
         <v>391</v>
       </c>
@@ -14178,7 +14170,7 @@
       </c>
       <c r="L377" s="11"/>
     </row>
-    <row r="378" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A378" s="12" t="s">
         <v>391</v>
       </c>
@@ -14208,7 +14200,7 @@
       <c r="K378" s="6"/>
       <c r="L378" s="11"/>
     </row>
-    <row r="379" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A379" s="12" t="s">
         <v>391</v>
       </c>
@@ -14238,7 +14230,7 @@
       <c r="K379" s="14"/>
       <c r="L379" s="15"/>
     </row>
-    <row r="380" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A380" s="12" t="s">
         <v>396</v>
       </c>
@@ -14266,7 +14258,7 @@
       </c>
       <c r="L380" s="8"/>
     </row>
-    <row r="381" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A381" s="12" t="s">
         <v>396</v>
       </c>
@@ -14294,7 +14286,7 @@
       </c>
       <c r="L381" s="11"/>
     </row>
-    <row r="382" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A382" s="12" t="s">
         <v>396</v>
       </c>
@@ -14324,7 +14316,7 @@
       </c>
       <c r="L382" s="11"/>
     </row>
-    <row r="383" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A383" s="12" t="s">
         <v>396</v>
       </c>
@@ -14354,7 +14346,7 @@
       </c>
       <c r="L383" s="11"/>
     </row>
-    <row r="384" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A384" s="12" t="s">
         <v>396</v>
       </c>
@@ -14382,7 +14374,7 @@
       </c>
       <c r="L384" s="11"/>
     </row>
-    <row r="385" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A385" s="12" t="s">
         <v>396</v>
       </c>
@@ -14410,7 +14402,7 @@
       </c>
       <c r="L385" s="15"/>
     </row>
-    <row r="386" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A386" s="12" t="s">
         <v>398</v>
       </c>
@@ -14440,7 +14432,7 @@
       </c>
       <c r="L386" s="8"/>
     </row>
-    <row r="387" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A387" s="12" t="s">
         <v>398</v>
       </c>
@@ -14470,7 +14462,7 @@
       </c>
       <c r="L387" s="11"/>
     </row>
-    <row r="388" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A388" s="12" t="s">
         <v>398</v>
       </c>
@@ -14500,7 +14492,7 @@
       </c>
       <c r="L388" s="11"/>
     </row>
-    <row r="389" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A389" s="12" t="s">
         <v>398</v>
       </c>
@@ -14524,7 +14516,7 @@
       </c>
       <c r="L389" s="11"/>
     </row>
-    <row r="390" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A390" s="12" t="s">
         <v>398</v>
       </c>
@@ -14550,7 +14542,7 @@
       </c>
       <c r="L390" s="11"/>
     </row>
-    <row r="391" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A391" s="12" t="s">
         <v>398</v>
       </c>
@@ -14578,7 +14570,7 @@
       </c>
       <c r="L391" s="15"/>
     </row>
-    <row r="392" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A392" s="12" t="s">
         <v>407</v>
       </c>
@@ -14604,7 +14596,7 @@
       <c r="K392" s="7"/>
       <c r="L392" s="8"/>
     </row>
-    <row r="393" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A393" s="12" t="s">
         <v>407</v>
       </c>
@@ -14630,7 +14622,7 @@
       <c r="K393" s="6"/>
       <c r="L393" s="11"/>
     </row>
-    <row r="394" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A394" s="12" t="s">
         <v>407</v>
       </c>
@@ -14656,7 +14648,7 @@
       </c>
       <c r="L394" s="11"/>
     </row>
-    <row r="395" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A395" s="12" t="s">
         <v>407</v>
       </c>
@@ -14686,7 +14678,7 @@
       </c>
       <c r="L395" s="11"/>
     </row>
-    <row r="396" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A396" s="12" t="s">
         <v>407</v>
       </c>
@@ -14716,7 +14708,7 @@
       </c>
       <c r="L396" s="11"/>
     </row>
-    <row r="397" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A397" s="12" t="s">
         <v>407</v>
       </c>
@@ -14746,7 +14738,7 @@
       </c>
       <c r="L397" s="15"/>
     </row>
-    <row r="398" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A398" s="12" t="s">
         <v>412</v>
       </c>
@@ -14755,9 +14747,15 @@
       </c>
       <c r="C398" s="6"/>
       <c r="D398" s="7"/>
-      <c r="E398" s="7"/>
-      <c r="F398" s="7"/>
-      <c r="G398" s="7"/>
+      <c r="E398" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="F398" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="G398" s="7" t="s">
+        <v>414</v>
+      </c>
       <c r="H398" s="7" t="s">
         <v>114</v>
       </c>
@@ -14770,7 +14768,7 @@
       </c>
       <c r="L398" s="8"/>
     </row>
-    <row r="399" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A399" s="12" t="s">
         <v>412</v>
       </c>
@@ -14779,16 +14777,16 @@
       </c>
       <c r="C399" s="6"/>
       <c r="D399" s="6"/>
-      <c r="E399" s="6"/>
+      <c r="E399" s="6" t="s">
+        <v>517</v>
+      </c>
       <c r="F399" s="6" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="G399" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="H399" s="6" t="s">
-        <v>415</v>
-      </c>
+      <c r="H399" s="6"/>
       <c r="I399" s="6"/>
       <c r="J399" s="6" t="s">
         <v>99</v>
@@ -14798,7 +14796,7 @@
       </c>
       <c r="L399" s="11"/>
     </row>
-    <row r="400" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A400" s="12" t="s">
         <v>412</v>
       </c>
@@ -14806,8 +14804,7 @@
         <v>20</v>
       </c>
       <c r="C400" s="6"/>
-      <c r="D400" s="6"/>
-      <c r="E400" s="6" t="s">
+      <c r="D400" s="6" t="s">
         <v>417</v>
       </c>
       <c r="F400" s="6" t="s">
@@ -14818,15 +14815,13 @@
       <c r="I400" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="J400" s="6" t="s">
-        <v>418</v>
-      </c>
+      <c r="J400" s="6"/>
       <c r="K400" s="6" t="s">
         <v>419</v>
       </c>
       <c r="L400" s="11"/>
     </row>
-    <row r="401" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A401" s="12" t="s">
         <v>412</v>
       </c>
@@ -14852,11 +14847,11 @@
         <v>418</v>
       </c>
       <c r="K401" s="6" t="s">
-        <v>422</v>
+        <v>535</v>
       </c>
       <c r="L401" s="11"/>
     </row>
-    <row r="402" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A402" s="12" t="s">
         <v>412</v>
       </c>
@@ -14864,7 +14859,9 @@
         <v>25</v>
       </c>
       <c r="C402" s="6"/>
-      <c r="D402" s="6"/>
+      <c r="D402" s="6" t="s">
+        <v>420</v>
+      </c>
       <c r="E402" s="6" t="s">
         <v>105</v>
       </c>
@@ -14881,12 +14878,10 @@
       <c r="J402" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="K402" s="6" t="s">
-        <v>423</v>
-      </c>
+      <c r="K402" s="6"/>
       <c r="L402" s="11"/>
     </row>
-    <row r="403" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A403" s="12" t="s">
         <v>412</v>
       </c>
@@ -14912,9 +14907,9 @@
       </c>
       <c r="L403" s="15"/>
     </row>
-    <row r="404" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A404" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B404" s="5" t="s">
         <v>13</v>
@@ -14932,9 +14927,9 @@
       <c r="K404" s="7"/>
       <c r="L404" s="8"/>
     </row>
-    <row r="405" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A405" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B405" s="10" t="s">
         <v>16</v>
@@ -14952,9 +14947,9 @@
       <c r="K405" s="6"/>
       <c r="L405" s="11"/>
     </row>
-    <row r="406" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A406" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B406" s="10" t="s">
         <v>20</v>
@@ -14974,9 +14969,9 @@
       <c r="K406" s="6"/>
       <c r="L406" s="11"/>
     </row>
-    <row r="407" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A407" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B407" s="10" t="s">
         <v>22</v>
@@ -14996,9 +14991,9 @@
       <c r="K407" s="6"/>
       <c r="L407" s="11"/>
     </row>
-    <row r="408" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A408" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B408" s="10" t="s">
         <v>25</v>
@@ -15016,9 +15011,9 @@
       <c r="K408" s="6"/>
       <c r="L408" s="11"/>
     </row>
-    <row r="409" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A409" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B409" s="13" t="s">
         <v>27</v>
@@ -15036,15 +15031,15 @@
       <c r="K409" s="14"/>
       <c r="L409" s="15"/>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410" s="19" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B410" s="20" t="s">
         <v>13</v>
       </c>
       <c r="C410" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D410" s="18" t="s">
         <v>60</v>
@@ -15060,25 +15055,25 @@
         <v>312</v>
       </c>
       <c r="I410" s="18" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J410" s="18" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="K410" s="18"/>
       <c r="L410" s="18" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411" s="19" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B411" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C411" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D411" s="6" t="s">
         <v>60</v>
@@ -15095,7 +15090,7 @@
       </c>
       <c r="I411" s="6"/>
       <c r="J411" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="K411" s="6" t="s">
         <v>312</v>
@@ -15104,15 +15099,15 @@
         <v>73</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" s="19" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B412" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C412" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D412" s="6" t="s">
         <v>60</v>
@@ -15126,25 +15121,25 @@
         <v>312</v>
       </c>
       <c r="I412" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J412" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="K412" s="6"/>
       <c r="L412" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" s="19" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B413" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C413" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D413" s="6" t="s">
         <v>60</v>
@@ -15161,22 +15156,22 @@
         <v>312</v>
       </c>
       <c r="J413" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="K413" s="6"/>
       <c r="L413" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" s="19" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B414" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C414" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D414" s="6" t="s">
         <v>60</v>
@@ -15193,22 +15188,22 @@
         <v>60</v>
       </c>
       <c r="J414" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="K414" s="6"/>
       <c r="L414" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="415" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A415" s="19" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B415" s="19" t="s">
         <v>27</v>
       </c>
       <c r="C415" s="14" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D415" s="21" t="s">
         <v>60</v>
@@ -15225,16 +15220,16 @@
         <v>60</v>
       </c>
       <c r="J415" s="21" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="K415" s="21"/>
       <c r="L415" s="21" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="416" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A416" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B416" s="5" t="s">
         <v>13</v>
@@ -15242,13 +15237,13 @@
       <c r="C416" s="6"/>
       <c r="D416" s="7"/>
       <c r="E416" s="7" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F416" s="7" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G416" s="7" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H416" s="7"/>
       <c r="I416" s="7"/>
@@ -15258,9 +15253,9 @@
       <c r="K416" s="7"/>
       <c r="L416" s="8"/>
     </row>
-    <row r="417" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A417" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B417" s="10" t="s">
         <v>16</v>
@@ -15268,41 +15263,41 @@
       <c r="C417" s="6"/>
       <c r="D417" s="6"/>
       <c r="E417" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F417" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="G417" s="6"/>
       <c r="H417" s="6"/>
       <c r="I417" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="J417" s="6" t="s">
         <v>393</v>
       </c>
       <c r="K417" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L417" s="11"/>
     </row>
-    <row r="418" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A418" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B418" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C418" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D418" s="6"/>
       <c r="E418" s="6"/>
       <c r="F418" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G418" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H418" s="6"/>
       <c r="I418" s="6"/>
@@ -15310,27 +15305,27 @@
         <v>393</v>
       </c>
       <c r="K418" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L418" s="11"/>
     </row>
-    <row r="419" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A419" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B419" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C419" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D419" s="6"/>
       <c r="E419" s="6"/>
       <c r="F419" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G419" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H419" s="6"/>
       <c r="I419" s="6" t="s">
@@ -15342,9 +15337,9 @@
       <c r="K419" s="6"/>
       <c r="L419" s="11"/>
     </row>
-    <row r="420" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A420" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B420" s="10" t="s">
         <v>25</v>
@@ -15353,10 +15348,10 @@
       <c r="D420" s="6"/>
       <c r="E420" s="6"/>
       <c r="F420" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G420" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H420" s="6"/>
       <c r="I420" s="6" t="s">
@@ -15368,9 +15363,9 @@
       <c r="K420" s="6"/>
       <c r="L420" s="11"/>
     </row>
-    <row r="421" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A421" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B421" s="13" t="s">
         <v>27</v>
@@ -15378,13 +15373,13 @@
       <c r="C421" s="14"/>
       <c r="D421" s="14"/>
       <c r="E421" s="14" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F421" s="14" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G421" s="14" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H421" s="14"/>
       <c r="I421" s="14" t="s">
@@ -15396,31 +15391,31 @@
       <c r="K421" s="14"/>
       <c r="L421" s="15"/>
     </row>
-    <row r="422" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A422" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B422" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C422" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D422" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E422" s="7"/>
       <c r="F422" s="7" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G422" s="7" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H422" s="7" t="s">
         <v>408</v>
       </c>
       <c r="I422" s="7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J422" s="7" t="s">
         <v>393</v>
@@ -15430,29 +15425,29 @@
         <v>46</v>
       </c>
     </row>
-    <row r="423" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A423" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B423" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D423" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E423" s="6"/>
       <c r="F423" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G423" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H423" s="6"/>
       <c r="I423" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J423" s="6" t="s">
         <v>393</v>
@@ -15462,26 +15457,26 @@
         <v>46</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A424" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B424" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C424" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D424" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E424" s="6"/>
       <c r="F424" s="6"/>
       <c r="G424" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H424" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I424" s="6"/>
       <c r="J424" s="6" t="s">
@@ -15492,27 +15487,27 @@
         <v>46</v>
       </c>
     </row>
-    <row r="425" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A425" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B425" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C425" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D425" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E425" s="6"/>
       <c r="F425" s="6"/>
       <c r="G425" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H425" s="6"/>
       <c r="I425" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J425" s="6" t="s">
         <v>393</v>
@@ -15522,27 +15517,27 @@
         <v>46</v>
       </c>
     </row>
-    <row r="426" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A426" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B426" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C426" s="6"/>
       <c r="D426" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E426" s="6" t="s">
         <v>408</v>
       </c>
       <c r="F426" s="6"/>
       <c r="G426" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H426" s="6"/>
       <c r="I426" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="J426" s="6" t="s">
         <v>393</v>
@@ -15552,23 +15547,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A427" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B427" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C427" s="14"/>
       <c r="D427" s="14" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E427" s="14" t="s">
         <v>408</v>
       </c>
       <c r="F427" s="14"/>
       <c r="G427" s="14" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H427" s="14"/>
       <c r="I427" s="14"/>
@@ -15580,9 +15575,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A428" s="12" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B428" s="5" t="s">
         <v>13</v>
@@ -15593,24 +15588,24 @@
         <v>399</v>
       </c>
       <c r="F428" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="G428" s="7" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H428" s="7"/>
       <c r="I428" s="7" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J428" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="8"/>
     </row>
-    <row r="429" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A429" s="12" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B429" s="10" t="s">
         <v>16</v>
@@ -15621,22 +15616,22 @@
         <v>399</v>
       </c>
       <c r="F429" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="G429" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H429" s="6"/>
       <c r="I429" s="6"/>
       <c r="J429" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="K429" s="6"/>
       <c r="L429" s="11"/>
     </row>
-    <row r="430" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A430" s="12" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B430" s="10" t="s">
         <v>20</v>
@@ -15647,24 +15642,24 @@
         <v>399</v>
       </c>
       <c r="F430" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G430" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H430" s="6"/>
       <c r="I430" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="J430" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="K430" s="6"/>
       <c r="L430" s="11"/>
     </row>
-    <row r="431" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A431" s="12" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B431" s="10" t="s">
         <v>22</v>
@@ -15673,24 +15668,24 @@
       <c r="D431" s="6"/>
       <c r="E431" s="6"/>
       <c r="F431" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G431" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H431" s="6"/>
       <c r="I431" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J431" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="K431" s="6"/>
       <c r="L431" s="11"/>
     </row>
-    <row r="432" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A432" s="12" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B432" s="10" t="s">
         <v>25</v>
@@ -15699,24 +15694,24 @@
       <c r="D432" s="6"/>
       <c r="E432" s="6"/>
       <c r="F432" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G432" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H432" s="6"/>
       <c r="I432" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J432" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="K432" s="6"/>
       <c r="L432" s="11"/>
     </row>
-    <row r="433" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A433" s="12" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B433" s="13" t="s">
         <v>27</v>
@@ -15726,21 +15721,21 @@
       <c r="E433" s="14"/>
       <c r="F433" s="14"/>
       <c r="G433" s="14" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H433" s="14"/>
       <c r="I433" s="14" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J433" s="14" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="K433" s="14"/>
       <c r="L433" s="15"/>
     </row>
-    <row r="434" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A434" s="12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B434" s="5" t="s">
         <v>13</v>
@@ -15749,28 +15744,28 @@
         <v>274</v>
       </c>
       <c r="D434" s="7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E434" s="7"/>
       <c r="F434" s="7" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G434" s="7"/>
       <c r="H434" s="7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I434" s="7"/>
       <c r="J434" s="7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="435" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A435" s="12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B435" s="10" t="s">
         <v>16</v>
@@ -15779,218 +15774,218 @@
         <v>277</v>
       </c>
       <c r="D435" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E435" s="6"/>
       <c r="F435" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="G435" s="6" t="s">
         <v>445</v>
       </c>
-      <c r="G435" s="6" t="s">
-        <v>447</v>
-      </c>
       <c r="H435" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I435" s="6"/>
       <c r="J435" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="K435" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="L435" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="436" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A436" s="12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B436" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C436" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D436" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E436" s="6"/>
       <c r="F436" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G436" s="6"/>
       <c r="H436" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I436" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="J436" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="K436" s="6"/>
       <c r="L436" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="437" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A437" s="12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B437" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C437" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D437" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E437" s="6"/>
       <c r="F437" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G437" s="6"/>
       <c r="H437" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I437" s="6" t="s">
         <v>312</v>
       </c>
       <c r="J437" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="K437" s="6"/>
       <c r="L437" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="438" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A438" s="12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B438" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C438" s="6"/>
       <c r="D438" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E438" s="6"/>
       <c r="F438" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G438" s="6"/>
       <c r="H438" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="I438" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="J438" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="K438" s="6"/>
       <c r="L438" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="439" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A439" s="12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B439" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C439" s="14"/>
       <c r="D439" s="14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E439" s="14"/>
       <c r="F439" s="14"/>
       <c r="G439" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="H439" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="I439" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="J439" s="14" t="s">
         <v>445</v>
-      </c>
-      <c r="H439" s="14" t="s">
-        <v>446</v>
-      </c>
-      <c r="I439" s="14" t="s">
-        <v>444</v>
-      </c>
-      <c r="J439" s="14" t="s">
-        <v>447</v>
       </c>
       <c r="K439" s="14"/>
       <c r="L439" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="440" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A440" s="12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B440" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C440" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D440" s="7"/>
       <c r="E440" s="7" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F440" s="7"/>
       <c r="G440" s="7" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H440" s="7" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I440" s="7"/>
       <c r="J440" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="K440" s="7" t="s">
         <v>452</v>
-      </c>
-      <c r="K440" s="7" t="s">
-        <v>454</v>
       </c>
       <c r="L440" s="8" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="441" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A441" s="12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B441" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C441" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D441" s="6"/>
       <c r="E441" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F441" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="G441" s="6"/>
       <c r="H441" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I441" s="6"/>
       <c r="J441" s="6"/>
       <c r="K441" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L441" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="442" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A442" s="12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B442" s="10" t="s">
         <v>20</v>
@@ -15999,20 +15994,20 @@
         <v>61</v>
       </c>
       <c r="D442" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E442" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F442" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G442" s="6"/>
       <c r="H442" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I442" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="J442" s="6"/>
       <c r="K442" s="6" t="s">
@@ -16022,31 +16017,31 @@
         <v>127</v>
       </c>
     </row>
-    <row r="443" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A443" s="12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B443" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D443" s="6"/>
       <c r="E443" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="F443" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="G443" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="H443" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="F443" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="G443" s="6" t="s">
-        <v>452</v>
-      </c>
-      <c r="H443" s="6" t="s">
+      <c r="I443" s="6" t="s">
         <v>453</v>
-      </c>
-      <c r="I443" s="6" t="s">
-        <v>455</v>
       </c>
       <c r="J443" s="6"/>
       <c r="K443" s="6" t="s">
@@ -16056,9 +16051,9 @@
         <v>127</v>
       </c>
     </row>
-    <row r="444" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A444" s="12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B444" s="10" t="s">
         <v>25</v>
@@ -16067,17 +16062,17 @@
         <v>397</v>
       </c>
       <c r="D444" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E444" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F444" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G444" s="6"/>
       <c r="H444" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I444" s="6"/>
       <c r="J444" s="6"/>
@@ -16088,9 +16083,9 @@
         <v>127</v>
       </c>
     </row>
-    <row r="445" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A445" s="12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B445" s="13" t="s">
         <v>27</v>
@@ -16100,15 +16095,15 @@
       </c>
       <c r="D445" s="14"/>
       <c r="E445" s="14" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F445" s="14" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="G445" s="14"/>
       <c r="H445" s="14"/>
       <c r="I445" s="14" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J445" s="14"/>
       <c r="K445" s="14" t="s">
@@ -16118,21 +16113,21 @@
         <v>127</v>
       </c>
     </row>
-    <row r="446" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A446" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B446" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C446" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="D446" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="E446" s="7" t="s">
         <v>457</v>
-      </c>
-      <c r="D446" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="E446" s="7" t="s">
-        <v>459</v>
       </c>
       <c r="F446" s="7" t="s">
         <v>404</v>
@@ -16140,31 +16135,31 @@
       <c r="G446" s="7"/>
       <c r="H446" s="7"/>
       <c r="I446" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J446" s="7"/>
       <c r="K446" s="7" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L446" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="447" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A447" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B447" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C447" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="D447" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="E447" s="6" t="s">
         <v>457</v>
-      </c>
-      <c r="D447" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="E447" s="6" t="s">
-        <v>459</v>
       </c>
       <c r="F447" s="6" t="s">
         <v>404</v>
@@ -16172,7 +16167,7 @@
       <c r="G447" s="6"/>
       <c r="H447" s="6"/>
       <c r="I447" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J447" s="6"/>
       <c r="K447" s="6" t="s">
@@ -16182,59 +16177,59 @@
         <v>55</v>
       </c>
     </row>
-    <row r="448" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A448" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B448" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C448" s="6"/>
       <c r="D448" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E448" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F448" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G448" s="6"/>
       <c r="H448" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I448" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J448" s="6"/>
       <c r="K448" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L448" s="11" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="449" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A449" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B449" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C449" s="6"/>
       <c r="D449" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E449" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F449" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G449" s="6"/>
       <c r="H449" s="6"/>
       <c r="I449" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J449" s="6"/>
       <c r="K449" s="6" t="s">
@@ -16244,27 +16239,27 @@
         <v>55</v>
       </c>
     </row>
-    <row r="450" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A450" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B450" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C450" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D450" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E450" s="6"/>
       <c r="F450" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G450" s="6"/>
       <c r="H450" s="6"/>
       <c r="I450" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J450" s="6"/>
       <c r="K450" s="6" t="s">
@@ -16274,27 +16269,27 @@
         <v>55</v>
       </c>
     </row>
-    <row r="451" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A451" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B451" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C451" s="14" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D451" s="14" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E451" s="14"/>
       <c r="F451" s="14" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G451" s="14"/>
       <c r="H451" s="14"/>
       <c r="I451" s="14" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J451" s="14"/>
       <c r="K451" s="14" t="s">
@@ -16304,9 +16299,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="452" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A452" s="12" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B452" s="5" t="s">
         <v>13</v>
@@ -16315,15 +16310,15 @@
         <v>84</v>
       </c>
       <c r="D452" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E452" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F452" s="7"/>
       <c r="G452" s="7"/>
       <c r="H452" s="7" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I452" s="7"/>
       <c r="J452" s="7" t="s">
@@ -16336,9 +16331,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="453" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A453" s="12" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B453" s="10" t="s">
         <v>16</v>
@@ -16347,13 +16342,13 @@
         <v>89</v>
       </c>
       <c r="D453" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E453" s="6"/>
       <c r="F453" s="6"/>
       <c r="G453" s="6"/>
       <c r="H453" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I453" s="6"/>
       <c r="J453" s="6" t="s">
@@ -16366,24 +16361,24 @@
         <v>119</v>
       </c>
     </row>
-    <row r="454" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A454" s="12" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B454" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C454" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D454" s="6"/>
       <c r="E454" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F454" s="6"/>
       <c r="G454" s="6"/>
       <c r="H454" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I454" s="6"/>
       <c r="J454" s="6" t="s">
@@ -16396,26 +16391,26 @@
         <v>119</v>
       </c>
     </row>
-    <row r="455" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A455" s="12" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B455" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C455" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D455" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="E455" s="6" t="s">
         <v>463</v>
-      </c>
-      <c r="E455" s="6" t="s">
-        <v>465</v>
       </c>
       <c r="F455" s="6"/>
       <c r="G455" s="6"/>
       <c r="H455" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I455" s="6"/>
       <c r="J455" s="6" t="s">
@@ -16428,9 +16423,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="456" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A456" s="12" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B456" s="10" t="s">
         <v>25</v>
@@ -16440,12 +16435,12 @@
       </c>
       <c r="D456" s="6"/>
       <c r="E456" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F456" s="6"/>
       <c r="G456" s="6"/>
       <c r="H456" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I456" s="6"/>
       <c r="J456" s="6" t="s">
@@ -16458,9 +16453,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="457" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A457" s="12" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B457" s="13" t="s">
         <v>27</v>
@@ -16469,15 +16464,15 @@
         <v>397</v>
       </c>
       <c r="D457" s="14" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E457" s="14"/>
       <c r="F457" s="14" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G457" s="14"/>
       <c r="H457" s="14" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="I457" s="14"/>
       <c r="J457" s="14" t="s">
@@ -16490,9 +16485,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="458" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A458" s="12" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B458" s="5" t="s">
         <v>13</v>
@@ -16500,7 +16495,7 @@
       <c r="C458" s="6"/>
       <c r="D458" s="7"/>
       <c r="E458" s="7" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F458" s="7"/>
       <c r="G458" s="7"/>
@@ -16510,9 +16505,9 @@
       <c r="K458" s="7"/>
       <c r="L458" s="8"/>
     </row>
-    <row r="459" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A459" s="12" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B459" s="10" t="s">
         <v>16</v>
@@ -16520,7 +16515,7 @@
       <c r="C459" s="6"/>
       <c r="D459" s="6"/>
       <c r="E459" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F459" s="6"/>
       <c r="G459" s="6"/>
@@ -16530,9 +16525,9 @@
       <c r="K459" s="6"/>
       <c r="L459" s="11"/>
     </row>
-    <row r="460" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A460" s="12" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B460" s="10" t="s">
         <v>20</v>
@@ -16540,10 +16535,10 @@
       <c r="C460" s="6"/>
       <c r="D460" s="6"/>
       <c r="E460" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F460" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G460" s="6"/>
       <c r="H460" s="6"/>
@@ -16552,9 +16547,9 @@
       <c r="K460" s="6"/>
       <c r="L460" s="11"/>
     </row>
-    <row r="461" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A461" s="12" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B461" s="10" t="s">
         <v>22</v>
@@ -16562,10 +16557,10 @@
       <c r="C461" s="6"/>
       <c r="D461" s="6"/>
       <c r="E461" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F461" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G461" s="6"/>
       <c r="H461" s="6"/>
@@ -16574,9 +16569,9 @@
       <c r="K461" s="6"/>
       <c r="L461" s="11"/>
     </row>
-    <row r="462" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A462" s="12" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B462" s="10" t="s">
         <v>25</v>
@@ -16585,7 +16580,7 @@
       <c r="D462" s="6"/>
       <c r="E462" s="6"/>
       <c r="F462" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G462" s="6"/>
       <c r="H462" s="6"/>
@@ -16594,9 +16589,9 @@
       <c r="K462" s="6"/>
       <c r="L462" s="11"/>
     </row>
-    <row r="463" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A463" s="12" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B463" s="13" t="s">
         <v>27</v>
@@ -16605,7 +16600,7 @@
       <c r="D463" s="14"/>
       <c r="E463" s="14"/>
       <c r="F463" s="14" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G463" s="14"/>
       <c r="H463" s="14"/>
@@ -16614,9 +16609,9 @@
       <c r="K463" s="14"/>
       <c r="L463" s="15"/>
     </row>
-    <row r="464" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A464" s="12" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B464" s="5" t="s">
         <v>13</v>
@@ -16624,7 +16619,7 @@
       <c r="C464" s="6"/>
       <c r="D464" s="7"/>
       <c r="E464" s="7" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F464" s="7" t="s">
         <v>239</v>
@@ -16634,19 +16629,19 @@
       </c>
       <c r="H464" s="7"/>
       <c r="I464" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="J464" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="K464" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="J464" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="K464" s="7" t="s">
-        <v>472</v>
-      </c>
       <c r="L464" s="8"/>
     </row>
-    <row r="465" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A465" s="12" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B465" s="10" t="s">
         <v>16</v>
@@ -16654,7 +16649,7 @@
       <c r="C465" s="6"/>
       <c r="D465" s="6"/>
       <c r="E465" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F465" s="6" t="s">
         <v>239</v>
@@ -16664,17 +16659,17 @@
       </c>
       <c r="H465" s="6"/>
       <c r="I465" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J465" s="6"/>
       <c r="K465" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="L465" s="11"/>
     </row>
-    <row r="466" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A466" s="12" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B466" s="10" t="s">
         <v>20</v>
@@ -16682,7 +16677,7 @@
       <c r="C466" s="6"/>
       <c r="D466" s="6"/>
       <c r="E466" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F466" s="6" t="s">
         <v>131</v>
@@ -16692,17 +16687,17 @@
       </c>
       <c r="H466" s="6"/>
       <c r="I466" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J466" s="6"/>
       <c r="K466" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L466" s="11"/>
     </row>
-    <row r="467" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A467" s="12" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B467" s="10" t="s">
         <v>22</v>
@@ -16710,7 +16705,7 @@
       <c r="C467" s="6"/>
       <c r="D467" s="6"/>
       <c r="E467" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F467" s="6" t="s">
         <v>131</v>
@@ -16722,13 +16717,13 @@
       <c r="I467" s="6"/>
       <c r="J467" s="6"/>
       <c r="K467" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L467" s="11"/>
     </row>
-    <row r="468" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A468" s="12" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B468" s="10" t="s">
         <v>25</v>
@@ -16736,7 +16731,7 @@
       <c r="C468" s="6"/>
       <c r="D468" s="6"/>
       <c r="E468" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F468" s="6" t="s">
         <v>131</v>
@@ -16754,9 +16749,9 @@
       <c r="K468" s="6"/>
       <c r="L468" s="11"/>
     </row>
-    <row r="469" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A469" s="12" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B469" s="13" t="s">
         <v>27</v>
@@ -16764,7 +16759,7 @@
       <c r="C469" s="14"/>
       <c r="D469" s="14"/>
       <c r="E469" s="14" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F469" s="14" t="s">
         <v>131</v>
@@ -16774,17 +16769,17 @@
       </c>
       <c r="H469" s="14"/>
       <c r="I469" s="14" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="J469" s="14" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K469" s="14"/>
       <c r="L469" s="15"/>
     </row>
-    <row r="470" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A470" s="12" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B470" s="5" t="s">
         <v>13</v>
@@ -16792,16 +16787,16 @@
       <c r="C470" s="6"/>
       <c r="D470" s="7"/>
       <c r="E470" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="F470" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="G470" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="H470" s="7" t="s">
         <v>479</v>
-      </c>
-      <c r="F470" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="G470" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="H470" s="7" t="s">
-        <v>481</v>
       </c>
       <c r="I470" s="7"/>
       <c r="J470" s="7" t="s">
@@ -16812,9 +16807,9 @@
       </c>
       <c r="L470" s="8"/>
     </row>
-    <row r="471" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A471" s="12" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B471" s="10" t="s">
         <v>16</v>
@@ -16823,14 +16818,14 @@
       <c r="D471" s="6"/>
       <c r="E471" s="6"/>
       <c r="F471" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G471" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="H471" s="6"/>
       <c r="I471" s="6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J471" s="6" t="s">
         <v>393</v>
@@ -16840,9 +16835,9 @@
       </c>
       <c r="L471" s="11"/>
     </row>
-    <row r="472" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A472" s="12" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B472" s="10" t="s">
         <v>20</v>
@@ -16852,16 +16847,16 @@
       </c>
       <c r="D472" s="6"/>
       <c r="E472" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="F472" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="G472" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="F472" s="6" t="s">
-        <v>484</v>
-      </c>
-      <c r="G472" s="6" t="s">
-        <v>485</v>
-      </c>
       <c r="H472" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="I472" s="6"/>
       <c r="J472" s="6" t="s">
@@ -16872,9 +16867,9 @@
       </c>
       <c r="L472" s="11"/>
     </row>
-    <row r="473" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A473" s="12" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B473" s="10" t="s">
         <v>22</v>
@@ -16884,17 +16879,17 @@
       </c>
       <c r="D473" s="6"/>
       <c r="E473" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="F473" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="F473" s="6" t="s">
-        <v>484</v>
-      </c>
       <c r="G473" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="H473" s="6"/>
       <c r="I473" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J473" s="6" t="s">
         <v>393</v>
@@ -16904,9 +16899,9 @@
       </c>
       <c r="L473" s="11"/>
     </row>
-    <row r="474" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A474" s="12" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B474" s="10" t="s">
         <v>25</v>
@@ -16916,13 +16911,13 @@
       </c>
       <c r="D474" s="6"/>
       <c r="E474" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F474" s="6"/>
       <c r="G474" s="6"/>
       <c r="H474" s="6"/>
       <c r="I474" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J474" s="6" t="s">
         <v>393</v>
@@ -16932,9 +16927,9 @@
       </c>
       <c r="L474" s="11"/>
     </row>
-    <row r="475" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A475" s="12" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B475" s="13" t="s">
         <v>27</v>
@@ -16944,15 +16939,15 @@
       </c>
       <c r="D475" s="14"/>
       <c r="E475" s="14" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F475" s="14" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G475" s="14"/>
       <c r="H475" s="14"/>
       <c r="I475" s="14" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J475" s="14" t="s">
         <v>393</v>
@@ -16962,9 +16957,9 @@
       </c>
       <c r="L475" s="15"/>
     </row>
-    <row r="476" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A476" s="12" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B476" s="5" t="s">
         <v>13</v>
@@ -16975,24 +16970,24 @@
         <v>399</v>
       </c>
       <c r="F476" s="7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="G476" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H476" s="7"/>
       <c r="I476" s="7" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J476" s="7"/>
       <c r="K476" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="L476" s="8"/>
     </row>
-    <row r="477" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A477" s="12" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B477" s="10" t="s">
         <v>16</v>
@@ -17004,21 +16999,21 @@
       </c>
       <c r="F477" s="6"/>
       <c r="G477" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="H477" s="6"/>
       <c r="I477" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J477" s="6"/>
       <c r="K477" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="L477" s="11"/>
     </row>
-    <row r="478" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A478" s="12" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B478" s="10" t="s">
         <v>20</v>
@@ -17032,15 +17027,15 @@
       <c r="G478" s="6"/>
       <c r="H478" s="6"/>
       <c r="I478" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J478" s="6"/>
       <c r="K478" s="6"/>
       <c r="L478" s="11"/>
     </row>
-    <row r="479" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A479" s="12" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B479" s="10" t="s">
         <v>22</v>
@@ -17048,11 +17043,11 @@
       <c r="C479" s="6"/>
       <c r="D479" s="6"/>
       <c r="E479" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F479" s="6"/>
       <c r="G479" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="H479" s="6"/>
       <c r="I479" s="6"/>
@@ -17060,9 +17055,9 @@
       <c r="K479" s="6"/>
       <c r="L479" s="11"/>
     </row>
-    <row r="480" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A480" s="12" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B480" s="10" t="s">
         <v>25</v>
@@ -17070,25 +17065,25 @@
       <c r="C480" s="6"/>
       <c r="D480" s="6"/>
       <c r="E480" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F480" s="6"/>
       <c r="G480" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="H480" s="6"/>
       <c r="I480" s="6"/>
       <c r="J480" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="K480" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="L480" s="11"/>
     </row>
-    <row r="481" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A481" s="12" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B481" s="13" t="s">
         <v>27</v>
@@ -17096,23 +17091,23 @@
       <c r="C481" s="14"/>
       <c r="D481" s="14"/>
       <c r="E481" s="14" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F481" s="14" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="G481" s="14"/>
       <c r="H481" s="14"/>
       <c r="I481" s="14"/>
       <c r="J481" s="14"/>
       <c r="K481" s="14" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="L481" s="15"/>
     </row>
-    <row r="482" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A482" s="12" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B482" s="5" t="s">
         <v>13</v>
@@ -17120,27 +17115,27 @@
       <c r="C482" s="6"/>
       <c r="D482" s="7"/>
       <c r="E482" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="F482" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="G482" s="7" t="s">
         <v>496</v>
-      </c>
-      <c r="F482" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="G482" s="7" t="s">
-        <v>498</v>
       </c>
       <c r="H482" s="7"/>
       <c r="I482" s="7"/>
       <c r="J482" s="7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="K482" s="7" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="L482" s="8"/>
     </row>
-    <row r="483" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A483" s="12" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B483" s="10" t="s">
         <v>16</v>
@@ -17148,23 +17143,23 @@
       <c r="C483" s="6"/>
       <c r="D483" s="6"/>
       <c r="E483" s="6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F483" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G483" s="6"/>
       <c r="H483" s="6"/>
       <c r="I483" s="6"/>
       <c r="J483" s="6"/>
       <c r="K483" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="L483" s="11"/>
     </row>
-    <row r="484" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A484" s="12" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B484" s="10" t="s">
         <v>20</v>
@@ -17172,23 +17167,23 @@
       <c r="C484" s="6"/>
       <c r="D484" s="6"/>
       <c r="E484" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F484" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="G484" s="6"/>
       <c r="H484" s="6"/>
       <c r="I484" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="J484" s="6"/>
       <c r="K484" s="6"/>
       <c r="L484" s="11"/>
     </row>
-    <row r="485" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A485" s="12" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B485" s="10" t="s">
         <v>22</v>
@@ -17206,9 +17201,9 @@
       <c r="K485" s="6"/>
       <c r="L485" s="11"/>
     </row>
-    <row r="486" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A486" s="12" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B486" s="10" t="s">
         <v>25</v>
@@ -17217,10 +17212,10 @@
       <c r="D486" s="6"/>
       <c r="E486" s="6"/>
       <c r="F486" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G486" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H486" s="6"/>
       <c r="I486" s="6" t="s">
@@ -17228,13 +17223,13 @@
       </c>
       <c r="J486" s="6"/>
       <c r="K486" s="6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="L486" s="11"/>
     </row>
-    <row r="487" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A487" s="12" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B487" s="13" t="s">
         <v>27</v>
@@ -17243,10 +17238,10 @@
       <c r="D487" s="14"/>
       <c r="E487" s="14"/>
       <c r="F487" s="14" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G487" s="14" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H487" s="14"/>
       <c r="I487" s="14" t="s">
@@ -17256,9 +17251,9 @@
       <c r="K487" s="14"/>
       <c r="L487" s="15"/>
     </row>
-    <row r="488" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A488" s="12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B488" s="5" t="s">
         <v>13</v>
@@ -17276,13 +17271,13 @@
       </c>
       <c r="J488" s="7"/>
       <c r="K488" s="7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L488" s="8"/>
     </row>
-    <row r="489" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A489" s="12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B489" s="10" t="s">
         <v>16</v>
@@ -17308,13 +17303,13 @@
       </c>
       <c r="J489" s="6"/>
       <c r="K489" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L489" s="11"/>
     </row>
-    <row r="490" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A490" s="12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B490" s="10" t="s">
         <v>20</v>
@@ -17338,13 +17333,13 @@
         <v>113</v>
       </c>
       <c r="K490" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L490" s="11"/>
     </row>
-    <row r="491" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A491" s="12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B491" s="10" t="s">
         <v>22</v>
@@ -17352,7 +17347,7 @@
       <c r="C491" s="6"/>
       <c r="D491" s="6"/>
       <c r="E491" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F491" s="6"/>
       <c r="G491" s="6" t="s">
@@ -17366,13 +17361,13 @@
       </c>
       <c r="J491" s="6"/>
       <c r="K491" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L491" s="11"/>
     </row>
-    <row r="492" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A492" s="12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B492" s="10" t="s">
         <v>25</v>
@@ -17380,7 +17375,7 @@
       <c r="C492" s="6"/>
       <c r="D492" s="6"/>
       <c r="E492" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F492" s="6" t="s">
         <v>128</v>
@@ -17394,13 +17389,13 @@
       <c r="I492" s="6"/>
       <c r="J492" s="6"/>
       <c r="K492" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L492" s="11"/>
     </row>
-    <row r="493" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A493" s="12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B493" s="13" t="s">
         <v>27</v>
@@ -17422,9 +17417,9 @@
       <c r="K493" s="14"/>
       <c r="L493" s="15"/>
     </row>
-    <row r="494" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A494" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B494" s="5" t="s">
         <v>13</v>
@@ -17450,9 +17445,9 @@
       </c>
       <c r="L494" s="8"/>
     </row>
-    <row r="495" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A495" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B495" s="10" t="s">
         <v>16</v>
@@ -17476,9 +17471,9 @@
       </c>
       <c r="L495" s="11"/>
     </row>
-    <row r="496" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A496" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B496" s="10" t="s">
         <v>20</v>
@@ -17500,13 +17495,13 @@
         <v>99</v>
       </c>
       <c r="K496" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L496" s="11"/>
     </row>
-    <row r="497" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A497" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B497" s="10" t="s">
         <v>22</v>
@@ -17528,13 +17523,13 @@
         <v>97</v>
       </c>
       <c r="K497" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L497" s="11"/>
     </row>
-    <row r="498" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A498" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B498" s="10" t="s">
         <v>25</v>
@@ -17554,13 +17549,13 @@
       </c>
       <c r="J498" s="6"/>
       <c r="K498" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L498" s="11"/>
     </row>
-    <row r="499" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A499" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B499" s="13" t="s">
         <v>27</v>
@@ -17584,9 +17579,9 @@
       </c>
       <c r="L499" s="15"/>
     </row>
-    <row r="500" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A500" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B500" s="5" t="s">
         <v>13</v>
@@ -17608,13 +17603,13 @@
         <v>121</v>
       </c>
       <c r="K500" s="7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L500" s="8"/>
     </row>
-    <row r="501" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A501" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B501" s="10" t="s">
         <v>16</v>
@@ -17636,13 +17631,13 @@
       </c>
       <c r="J501" s="6"/>
       <c r="K501" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L501" s="11"/>
     </row>
-    <row r="502" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A502" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B502" s="10" t="s">
         <v>20</v>
@@ -17664,13 +17659,13 @@
       <c r="I502" s="6"/>
       <c r="J502" s="6"/>
       <c r="K502" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L502" s="11"/>
     </row>
-    <row r="503" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A503" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B503" s="10" t="s">
         <v>22</v>
@@ -17694,13 +17689,13 @@
         <v>128</v>
       </c>
       <c r="K503" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L503" s="11"/>
     </row>
-    <row r="504" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A504" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B504" s="10" t="s">
         <v>25</v>
@@ -17720,13 +17715,13 @@
         <v>88</v>
       </c>
       <c r="K504" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L504" s="11"/>
     </row>
-    <row r="505" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A505" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B505" s="13" t="s">
         <v>27</v>
@@ -17748,9 +17743,9 @@
       <c r="K505" s="14"/>
       <c r="L505" s="15"/>
     </row>
-    <row r="506" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A506" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B506" s="5" t="s">
         <v>13</v>
@@ -17758,10 +17753,10 @@
       <c r="C506" s="6"/>
       <c r="D506" s="7"/>
       <c r="E506" s="7" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F506" s="7" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G506" s="7" t="s">
         <v>104</v>
@@ -17771,14 +17766,14 @@
       </c>
       <c r="I506" s="7"/>
       <c r="J506" s="7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="K506" s="7"/>
       <c r="L506" s="8"/>
     </row>
-    <row r="507" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A507" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B507" s="10" t="s">
         <v>16</v>
@@ -17786,10 +17781,10 @@
       <c r="C507" s="6"/>
       <c r="D507" s="6"/>
       <c r="E507" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F507" s="6" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G507" s="6" t="s">
         <v>82</v>
@@ -17799,27 +17794,27 @@
       </c>
       <c r="I507" s="6"/>
       <c r="J507" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="K507" s="6"/>
       <c r="L507" s="11"/>
     </row>
-    <row r="508" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A508" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B508" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C508" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D508" s="6"/>
       <c r="E508" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F508" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G508" s="6"/>
       <c r="H508" s="6" t="s">
@@ -17827,27 +17822,27 @@
       </c>
       <c r="I508" s="6"/>
       <c r="J508" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="K508" s="6"/>
       <c r="L508" s="11"/>
     </row>
-    <row r="509" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A509" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B509" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C509" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D509" s="6"/>
       <c r="E509" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F509" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G509" s="6" t="s">
         <v>120</v>
@@ -17857,14 +17852,14 @@
       </c>
       <c r="I509" s="6"/>
       <c r="J509" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="K509" s="6"/>
       <c r="L509" s="11"/>
     </row>
-    <row r="510" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A510" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B510" s="10" t="s">
         <v>25</v>
@@ -17872,10 +17867,10 @@
       <c r="C510" s="6"/>
       <c r="D510" s="6"/>
       <c r="E510" s="6" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F510" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G510" s="6" t="s">
         <v>119</v>
@@ -17885,14 +17880,14 @@
       </c>
       <c r="I510" s="6"/>
       <c r="J510" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="K510" s="6"/>
       <c r="L510" s="11"/>
     </row>
-    <row r="511" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A511" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B511" s="13" t="s">
         <v>27</v>
@@ -17900,10 +17895,10 @@
       <c r="C511" s="14"/>
       <c r="D511" s="14"/>
       <c r="E511" s="14" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F511" s="14" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G511" s="14" t="s">
         <v>127</v>
@@ -17913,14 +17908,14 @@
       </c>
       <c r="I511" s="14"/>
       <c r="J511" s="14" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="K511" s="14"/>
       <c r="L511" s="15"/>
     </row>
-    <row r="512" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A512" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B512" s="5" t="s">
         <v>13</v>
@@ -17930,25 +17925,25 @@
       </c>
       <c r="D512" s="7"/>
       <c r="E512" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F512" s="7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G512" s="7"/>
       <c r="H512" s="7"/>
       <c r="I512" s="7" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="J512" s="7"/>
       <c r="K512" s="7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L512" s="8"/>
     </row>
-    <row r="513" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A513" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B513" s="10" t="s">
         <v>16</v>
@@ -17958,10 +17953,10 @@
       </c>
       <c r="D513" s="6"/>
       <c r="E513" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F513" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G513" s="6"/>
       <c r="H513" s="6"/>
@@ -17970,13 +17965,13 @@
         <v>417</v>
       </c>
       <c r="K513" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L513" s="11"/>
     </row>
-    <row r="514" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A514" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B514" s="10" t="s">
         <v>20</v>
@@ -17985,10 +17980,10 @@
         <v>61</v>
       </c>
       <c r="D514" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E514" s="6" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F514" s="6"/>
       <c r="G514" s="6" t="s">
@@ -17996,17 +17991,17 @@
       </c>
       <c r="H514" s="6"/>
       <c r="I514" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="J514" s="6"/>
       <c r="K514" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L514" s="11"/>
     </row>
-    <row r="515" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A515" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B515" s="10" t="s">
         <v>22</v>
@@ -18016,10 +18011,10 @@
         <v>420</v>
       </c>
       <c r="E515" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F515" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="G515" s="6"/>
       <c r="H515" s="6" t="s">
@@ -18027,16 +18022,16 @@
       </c>
       <c r="I515" s="6"/>
       <c r="J515" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="K515" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L515" s="11"/>
     </row>
-    <row r="516" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A516" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B516" s="10" t="s">
         <v>25</v>
@@ -18058,13 +18053,13 @@
         <v>115</v>
       </c>
       <c r="K516" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L516" s="11"/>
     </row>
-    <row r="517" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A517" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B517" s="13" t="s">
         <v>27</v>
@@ -18080,9 +18075,9 @@
       <c r="K517" s="14"/>
       <c r="L517" s="15"/>
     </row>
-    <row r="518" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A518" s="12" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B518" s="5" t="s">
         <v>13</v>
@@ -18092,25 +18087,25 @@
       </c>
       <c r="D518" s="7"/>
       <c r="E518" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F518" s="7" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G518" s="7" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H518" s="7"/>
       <c r="I518" s="7"/>
       <c r="J518" s="7"/>
       <c r="K518" s="7" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L518" s="8"/>
     </row>
-    <row r="519" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A519" s="12" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B519" s="10" t="s">
         <v>16</v>
@@ -18126,19 +18121,19 @@
       <c r="G519" s="6"/>
       <c r="H519" s="6"/>
       <c r="I519" s="6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="J519" s="6" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="K519" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L519" s="11"/>
     </row>
-    <row r="520" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A520" s="12" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B520" s="10" t="s">
         <v>20</v>
@@ -18151,7 +18146,7 @@
       </c>
       <c r="E520" s="6"/>
       <c r="F520" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="G520" s="6"/>
       <c r="H520" s="6"/>
@@ -18160,43 +18155,43 @@
         <v>96</v>
       </c>
       <c r="K520" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L520" s="11"/>
     </row>
-    <row r="521" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A521" s="12" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B521" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C521" s="6"/>
       <c r="D521" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E521" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F521" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="G521" s="6"/>
       <c r="H521" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="I521" s="6"/>
       <c r="J521" s="6" t="s">
         <v>420</v>
       </c>
       <c r="K521" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L521" s="11"/>
     </row>
-    <row r="522" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A522" s="12" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B522" s="10" t="s">
         <v>25</v>
@@ -18204,27 +18199,27 @@
       <c r="C522" s="6"/>
       <c r="D522" s="6"/>
       <c r="E522" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F522" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G522" s="6"/>
       <c r="H522" s="6" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="I522" s="6" t="s">
         <v>417</v>
       </c>
       <c r="J522" s="6"/>
       <c r="K522" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L522" s="11"/>
     </row>
-    <row r="523" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A523" s="12" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B523" s="13" t="s">
         <v>27</v>
@@ -18241,14 +18236,14 @@
       </c>
       <c r="I523" s="14"/>
       <c r="J523" s="14" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="K523" s="14"/>
       <c r="L523" s="15"/>
     </row>
-    <row r="524" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A524" s="22" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B524" s="5" t="s">
         <v>13</v>
@@ -18276,9 +18271,9 @@
       </c>
       <c r="L524" s="8"/>
     </row>
-    <row r="525" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A525" s="22" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B525" s="10" t="s">
         <v>16</v>
@@ -18304,9 +18299,9 @@
       </c>
       <c r="L525" s="11"/>
     </row>
-    <row r="526" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A526" s="22" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B526" s="10" t="s">
         <v>20</v>
@@ -18332,9 +18327,9 @@
       </c>
       <c r="L526" s="11"/>
     </row>
-    <row r="527" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A527" s="22" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B527" s="10" t="s">
         <v>22</v>
@@ -18360,9 +18355,9 @@
       <c r="K527" s="6"/>
       <c r="L527" s="11"/>
     </row>
-    <row r="528" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A528" s="22" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B528" s="10" t="s">
         <v>25</v>
@@ -18390,9 +18385,9 @@
       </c>
       <c r="L528" s="11"/>
     </row>
-    <row r="529" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A529" s="22" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B529" s="19" t="s">
         <v>27</v>
@@ -18420,9 +18415,9 @@
       </c>
       <c r="L529" s="23"/>
     </row>
-    <row r="530" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A530" s="12" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B530" s="5" t="s">
         <v>13</v>
@@ -18430,7 +18425,7 @@
       <c r="C530" s="5"/>
       <c r="D530" s="5"/>
       <c r="E530" s="5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F530" s="5" t="s">
         <v>113</v>
@@ -18448,9 +18443,9 @@
       <c r="K530" s="5"/>
       <c r="L530" s="24"/>
     </row>
-    <row r="531" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A531" s="12" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B531" s="10" t="s">
         <v>16</v>
@@ -18476,9 +18471,9 @@
       </c>
       <c r="L531" s="25"/>
     </row>
-    <row r="532" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A532" s="12" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B532" s="10" t="s">
         <v>20</v>
@@ -18504,9 +18499,9 @@
       </c>
       <c r="L532" s="25"/>
     </row>
-    <row r="533" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A533" s="12" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B533" s="10" t="s">
         <v>22</v>
@@ -18534,9 +18529,9 @@
       </c>
       <c r="L533" s="25"/>
     </row>
-    <row r="534" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A534" s="12" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B534" s="10" t="s">
         <v>25</v>
@@ -18551,7 +18546,7 @@
         <v>96</v>
       </c>
       <c r="H534" s="10" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="I534" s="10" t="s">
         <v>112</v>
@@ -18562,32 +18557,32 @@
       <c r="K534" s="10"/>
       <c r="L534" s="25"/>
     </row>
-    <row r="535" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A535" s="12" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B535" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C535" s="13"/>
       <c r="D535" s="13"/>
-      <c r="E535" s="13" t="s">
+      <c r="E535" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="F535" s="13" t="s">
+      <c r="F535" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="G535" s="13" t="s">
-        <v>535</v>
-      </c>
-      <c r="H535" s="13" t="s">
-        <v>536</v>
-      </c>
-      <c r="I535" s="13" t="s">
+      <c r="G535" s="27" t="s">
+        <v>533</v>
+      </c>
+      <c r="H535" s="27" t="s">
+        <v>534</v>
+      </c>
+      <c r="I535" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="J535" s="13"/>
-      <c r="K535" s="13" t="s">
+      <c r="J535" s="27"/>
+      <c r="K535" s="27" t="s">
         <v>99</v>
       </c>
       <c r="L535" s="26"/>

--- a/TT_apr26.xlsx
+++ b/TT_apr26.xlsx
@@ -1,34 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ittea\.gemini\antigravity\scratch\substitution26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACF4FE7-1508-4338-98C8-F0F4A0780318}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38967253-8324-4E77-B490-EDA727D205FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{87749542-9008-4FB2-99EF-E6484056E6E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{87749542-9008-4FB2-99EF-E6484056E6E3}"/>
   </bookViews>
   <sheets>
     <sheet name="TT_Apr26" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TT_Apr26!$A$1:$L$535</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4409" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4420" uniqueCount="535">
   <si>
     <t>tname</t>
   </si>
@@ -1296,6 +1302,9 @@
     <t>5B</t>
   </si>
   <si>
+    <t>SUPW4</t>
+  </si>
+  <si>
     <t>ADITI SABARWAL</t>
   </si>
   <si>
@@ -1560,9 +1569,6 @@
     <t>10 E</t>
   </si>
   <si>
-    <t>10 F</t>
-  </si>
-  <si>
     <t>10 H</t>
   </si>
   <si>
@@ -1633,9 +1639,6 @@
   </si>
   <si>
     <t>7A-LIB</t>
-  </si>
-  <si>
-    <t>CT 3B</t>
   </si>
 </sst>
 </file>
@@ -1896,7 +1899,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1950,9 +1953,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2268,22 +2268,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF073B80-F741-476C-ABC5-43118BEB6522}">
   <dimension ref="A1:L535"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" customWidth="1"/>
-    <col min="9" max="9" width="12.109375" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" customWidth="1"/>
-    <col min="11" max="12" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" customWidth="1"/>
+    <col min="11" max="12" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
@@ -2343,7 +2343,7 @@
       <c r="K2" s="7"/>
       <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>12</v>
       </c>
@@ -2367,7 +2367,7 @@
       <c r="K3" s="6"/>
       <c r="L3" s="11"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
@@ -2387,7 +2387,7 @@
       <c r="K4" s="6"/>
       <c r="L4" s="11"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>12</v>
       </c>
@@ -2409,7 +2409,7 @@
       <c r="K5" s="6"/>
       <c r="L5" s="11"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
@@ -2429,7 +2429,7 @@
       <c r="K6" s="6"/>
       <c r="L6" s="11"/>
     </row>
-    <row r="7" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>12</v>
       </c>
@@ -2451,7 +2451,7 @@
       <c r="K7" s="14"/>
       <c r="L7" s="15"/>
     </row>
-    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>30</v>
       </c>
@@ -2475,7 +2475,7 @@
       <c r="K8" s="7"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>30</v>
       </c>
@@ -2499,7 +2499,7 @@
       <c r="K9" s="6"/>
       <c r="L9" s="11"/>
     </row>
-    <row r="10" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>30</v>
       </c>
@@ -2523,7 +2523,7 @@
       <c r="K10" s="6"/>
       <c r="L10" s="11"/>
     </row>
-    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>30</v>
       </c>
@@ -2545,7 +2545,7 @@
       <c r="K11" s="6"/>
       <c r="L11" s="11"/>
     </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>30</v>
       </c>
@@ -2569,7 +2569,7 @@
       <c r="K12" s="6"/>
       <c r="L12" s="11"/>
     </row>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
         <v>30</v>
       </c>
@@ -2591,7 +2591,7 @@
       <c r="K13" s="14"/>
       <c r="L13" s="15"/>
     </row>
-    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>42</v>
       </c>
@@ -2623,7 +2623,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>42</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>42</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>42</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>42</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
         <v>42</v>
       </c>
@@ -2777,7 +2777,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>49</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
         <v>49</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>49</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>49</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>49</v>
       </c>
@@ -2945,7 +2945,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>49</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>56</v>
       </c>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="L26" s="8"/>
     </row>
-    <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
         <v>56</v>
       </c>
@@ -3029,7 +3029,7 @@
       <c r="K27" s="6"/>
       <c r="L27" s="11"/>
     </row>
-    <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>56</v>
       </c>
@@ -3059,7 +3059,7 @@
       <c r="K28" s="6"/>
       <c r="L28" s="11"/>
     </row>
-    <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>56</v>
       </c>
@@ -3085,7 +3085,7 @@
       <c r="K29" s="6"/>
       <c r="L29" s="11"/>
     </row>
-    <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
         <v>56</v>
       </c>
@@ -3113,7 +3113,7 @@
       <c r="K30" s="6"/>
       <c r="L30" s="11"/>
     </row>
-    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
         <v>56</v>
       </c>
@@ -3141,7 +3141,7 @@
       <c r="K31" s="14"/>
       <c r="L31" s="15"/>
     </row>
-    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
         <v>62</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
         <v>62</v>
       </c>
@@ -3201,7 +3201,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
         <v>62</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
         <v>62</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
         <v>62</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
         <v>62</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>68</v>
       </c>
@@ -3345,6 +3345,7 @@
       <c r="E38" s="7" t="s">
         <v>71</v>
       </c>
+      <c r="F38" s="6"/>
       <c r="G38" s="7" t="s">
         <v>72</v>
       </c>
@@ -3362,7 +3363,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
         <v>68</v>
       </c>
@@ -3396,7 +3397,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
         <v>68</v>
       </c>
@@ -3430,7 +3431,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
         <v>68</v>
       </c>
@@ -3464,7 +3465,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
         <v>68</v>
       </c>
@@ -3496,7 +3497,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
         <v>68</v>
       </c>
@@ -3530,7 +3531,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
         <v>76</v>
       </c>
@@ -3562,7 +3563,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
         <v>76</v>
       </c>
@@ -3596,7 +3597,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
         <v>76</v>
       </c>
@@ -3630,7 +3631,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
         <v>76</v>
       </c>
@@ -3664,7 +3665,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
         <v>76</v>
       </c>
@@ -3698,7 +3699,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
         <v>76</v>
       </c>
@@ -3732,7 +3733,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
         <v>83</v>
       </c>
@@ -3764,7 +3765,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
         <v>83</v>
       </c>
@@ -3796,7 +3797,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
         <v>83</v>
       </c>
@@ -3828,7 +3829,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
         <v>83</v>
       </c>
@@ -3860,7 +3861,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
         <v>83</v>
       </c>
@@ -3892,7 +3893,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
         <v>83</v>
       </c>
@@ -3924,7 +3925,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>94</v>
       </c>
@@ -3958,7 +3959,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
         <v>94</v>
       </c>
@@ -3992,7 +3993,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
         <v>94</v>
       </c>
@@ -4024,7 +4025,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
         <v>94</v>
       </c>
@@ -4054,7 +4055,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
         <v>94</v>
       </c>
@@ -4086,7 +4087,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
         <v>94</v>
       </c>
@@ -4118,7 +4119,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
         <v>103</v>
       </c>
@@ -4148,7 +4149,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="12" t="s">
         <v>103</v>
       </c>
@@ -4182,7 +4183,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="12" t="s">
         <v>103</v>
       </c>
@@ -4212,7 +4213,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="12" t="s">
         <v>103</v>
       </c>
@@ -4244,7 +4245,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
         <v>103</v>
       </c>
@@ -4276,7 +4277,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="12" t="s">
         <v>103</v>
       </c>
@@ -4308,7 +4309,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
         <v>110</v>
       </c>
@@ -4340,7 +4341,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="s">
         <v>110</v>
       </c>
@@ -4372,7 +4373,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
         <v>110</v>
       </c>
@@ -4404,7 +4405,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
         <v>110</v>
       </c>
@@ -4436,7 +4437,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
         <v>110</v>
       </c>
@@ -4468,7 +4469,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="9" t="s">
         <v>110</v>
       </c>
@@ -4498,7 +4499,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
         <v>116</v>
       </c>
@@ -4532,7 +4533,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
         <v>116</v>
       </c>
@@ -4566,7 +4567,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>116</v>
       </c>
@@ -4600,7 +4601,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
         <v>116</v>
       </c>
@@ -4634,7 +4635,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
         <v>116</v>
       </c>
@@ -4666,7 +4667,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="12" t="s">
         <v>116</v>
       </c>
@@ -4700,7 +4701,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
         <v>123</v>
       </c>
@@ -4732,7 +4733,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
         <v>123</v>
       </c>
@@ -4762,7 +4763,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
         <v>123</v>
       </c>
@@ -4792,7 +4793,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="12" t="s">
         <v>123</v>
       </c>
@@ -4824,7 +4825,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
         <v>123</v>
       </c>
@@ -4856,7 +4857,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="12" t="s">
         <v>123</v>
       </c>
@@ -4888,7 +4889,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="12" t="s">
         <v>129</v>
       </c>
@@ -4922,7 +4923,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
         <v>129</v>
       </c>
@@ -4956,7 +4957,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
         <v>129</v>
       </c>
@@ -4990,7 +4991,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="12" t="s">
         <v>129</v>
       </c>
@@ -5022,7 +5023,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="12" t="s">
         <v>129</v>
       </c>
@@ -5054,7 +5055,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="12" t="s">
         <v>129</v>
       </c>
@@ -5086,7 +5087,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="12" t="s">
         <v>134</v>
       </c>
@@ -5118,7 +5119,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="12" t="s">
         <v>134</v>
       </c>
@@ -5134,10 +5135,9 @@
       <c r="E93" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="F93" s="6" t="s">
+      <c r="G93" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="G93" s="6"/>
       <c r="H93" s="6"/>
       <c r="I93" s="6"/>
       <c r="J93" s="6" t="s">
@@ -5150,7 +5150,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="12" t="s">
         <v>134</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="12" t="s">
         <v>134</v>
       </c>
@@ -5216,7 +5216,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="12" t="s">
         <v>134</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="12" t="s">
         <v>134</v>
       </c>
@@ -5282,7 +5282,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="9" t="s">
         <v>138</v>
       </c>
@@ -5316,7 +5316,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="9" t="s">
         <v>138</v>
       </c>
@@ -5348,7 +5348,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
         <v>138</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="9" t="s">
         <v>138</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="9" t="s">
         <v>138</v>
       </c>
@@ -5444,7 +5444,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9" t="s">
         <v>138</v>
       </c>
@@ -5476,7 +5476,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="12" t="s">
         <v>141</v>
       </c>
@@ -5508,7 +5508,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="12" t="s">
         <v>141</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="12" t="s">
         <v>141</v>
       </c>
@@ -5574,7 +5574,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="12" t="s">
         <v>141</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="12" t="s">
         <v>141</v>
       </c>
@@ -5638,7 +5638,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="12" t="s">
         <v>141</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="12" t="s">
         <v>145</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="12" t="s">
         <v>145</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="12" t="s">
         <v>145</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="12" t="s">
         <v>145</v>
       </c>
@@ -5804,7 +5804,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="12" t="s">
         <v>145</v>
       </c>
@@ -5834,7 +5834,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="12" t="s">
         <v>145</v>
       </c>
@@ -5868,7 +5868,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="12" t="s">
         <v>149</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="12" t="s">
         <v>149</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="12" t="s">
         <v>149</v>
       </c>
@@ -5966,7 +5966,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="12" t="s">
         <v>149</v>
       </c>
@@ -5996,7 +5996,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="12" t="s">
         <v>149</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="12" t="s">
         <v>149</v>
       </c>
@@ -6064,7 +6064,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="12" t="s">
         <v>153</v>
       </c>
@@ -6096,7 +6096,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="12" t="s">
         <v>153</v>
       </c>
@@ -6130,7 +6130,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="12" t="s">
         <v>153</v>
       </c>
@@ -6162,7 +6162,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="12" t="s">
         <v>153</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="12" t="s">
         <v>153</v>
       </c>
@@ -6226,7 +6226,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="12" t="s">
         <v>153</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="12" t="s">
         <v>161</v>
       </c>
@@ -6292,7 +6292,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="12" t="s">
         <v>161</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="12" t="s">
         <v>161</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="12" t="s">
         <v>161</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="12" t="s">
         <v>161</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="12" t="s">
         <v>161</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="12" t="s">
         <v>167</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="12" t="s">
         <v>167</v>
       </c>
@@ -6518,7 +6518,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="12" t="s">
         <v>167</v>
       </c>
@@ -6552,7 +6552,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="12" t="s">
         <v>167</v>
       </c>
@@ -6586,7 +6586,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="12" t="s">
         <v>167</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="12" t="s">
         <v>167</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>175</v>
       </c>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="L140" s="8"/>
     </row>
-    <row r="141" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>175</v>
       </c>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="L141" s="11"/>
     </row>
-    <row r="142" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>175</v>
       </c>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="L142" s="11"/>
     </row>
-    <row r="143" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>175</v>
       </c>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="L143" s="11"/>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>175</v>
       </c>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="L144" s="11"/>
     </row>
-    <row r="145" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="12" t="s">
         <v>175</v>
       </c>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="L145" s="15"/>
     </row>
-    <row r="146" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="12" t="s">
         <v>182</v>
       </c>
@@ -6864,7 +6864,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="12" t="s">
         <v>182</v>
       </c>
@@ -6896,7 +6896,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="12" t="s">
         <v>182</v>
       </c>
@@ -6930,7 +6930,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="12" t="s">
         <v>182</v>
       </c>
@@ -6964,7 +6964,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="12" t="s">
         <v>182</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="12" t="s">
         <v>182</v>
       </c>
@@ -7028,7 +7028,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="12" t="s">
         <v>188</v>
       </c>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="L152" s="8"/>
     </row>
-    <row r="153" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="12" t="s">
         <v>188</v>
       </c>
@@ -7082,7 +7082,7 @@
       <c r="K153" s="6"/>
       <c r="L153" s="11"/>
     </row>
-    <row r="154" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="12" t="s">
         <v>188</v>
       </c>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="L154" s="11"/>
     </row>
-    <row r="155" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="12" t="s">
         <v>188</v>
       </c>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="L155" s="11"/>
     </row>
-    <row r="156" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="12" t="s">
         <v>188</v>
       </c>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="L156" s="11"/>
     </row>
-    <row r="157" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="12" t="s">
         <v>188</v>
       </c>
@@ -7190,7 +7190,7 @@
       <c r="K157" s="14"/>
       <c r="L157" s="15"/>
     </row>
-    <row r="158" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="12" t="s">
         <v>192</v>
       </c>
@@ -7224,7 +7224,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="12" t="s">
         <v>192</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="12" t="s">
         <v>192</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="12" t="s">
         <v>192</v>
       </c>
@@ -7322,7 +7322,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="12" t="s">
         <v>192</v>
       </c>
@@ -7356,7 +7356,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="12" t="s">
         <v>192</v>
       </c>
@@ -7386,7 +7386,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="12" t="s">
         <v>196</v>
       </c>
@@ -7399,6 +7399,7 @@
       <c r="D164" s="7" t="s">
         <v>65</v>
       </c>
+      <c r="E164" s="6"/>
       <c r="F164" s="7" t="s">
         <v>120</v>
       </c>
@@ -7415,7 +7416,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="12" t="s">
         <v>196</v>
       </c>
@@ -7447,7 +7448,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="12" t="s">
         <v>196</v>
       </c>
@@ -7481,7 +7482,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="12" t="s">
         <v>196</v>
       </c>
@@ -7515,7 +7516,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="12" t="s">
         <v>196</v>
       </c>
@@ -7549,7 +7550,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="12" t="s">
         <v>196</v>
       </c>
@@ -7581,7 +7582,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="12" t="s">
         <v>198</v>
       </c>
@@ -7613,7 +7614,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="12" t="s">
         <v>198</v>
       </c>
@@ -7645,7 +7646,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="12" t="s">
         <v>198</v>
       </c>
@@ -7679,7 +7680,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="12" t="s">
         <v>198</v>
       </c>
@@ -7713,7 +7714,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="12" t="s">
         <v>198</v>
       </c>
@@ -7745,7 +7746,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="12" t="s">
         <v>198</v>
       </c>
@@ -7777,7 +7778,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="12" t="s">
         <v>200</v>
       </c>
@@ -7809,7 +7810,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="12" t="s">
         <v>200</v>
       </c>
@@ -7843,7 +7844,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="12" t="s">
         <v>200</v>
       </c>
@@ -7875,7 +7876,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="12" t="s">
         <v>200</v>
       </c>
@@ -7909,7 +7910,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="12" t="s">
         <v>200</v>
       </c>
@@ -7941,7 +7942,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="12" t="s">
         <v>200</v>
       </c>
@@ -7973,7 +7974,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="12" t="s">
         <v>202</v>
       </c>
@@ -8005,7 +8006,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="12" t="s">
         <v>202</v>
       </c>
@@ -8039,7 +8040,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="12" t="s">
         <v>202</v>
       </c>
@@ -8071,7 +8072,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="12" t="s">
         <v>202</v>
       </c>
@@ -8105,7 +8106,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="12" t="s">
         <v>202</v>
       </c>
@@ -8139,7 +8140,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="12" t="s">
         <v>202</v>
       </c>
@@ -8173,7 +8174,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="12" t="s">
         <v>206</v>
       </c>
@@ -8205,7 +8206,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="12" t="s">
         <v>206</v>
       </c>
@@ -8239,7 +8240,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="12" t="s">
         <v>206</v>
       </c>
@@ -8273,7 +8274,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="12" t="s">
         <v>206</v>
       </c>
@@ -8305,7 +8306,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="12" t="s">
         <v>206</v>
       </c>
@@ -8339,7 +8340,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="12" t="s">
         <v>206</v>
       </c>
@@ -8371,7 +8372,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="12" t="s">
         <v>209</v>
       </c>
@@ -8405,7 +8406,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="12" t="s">
         <v>209</v>
       </c>
@@ -8435,7 +8436,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="12" t="s">
         <v>209</v>
       </c>
@@ -8467,7 +8468,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="12" t="s">
         <v>209</v>
       </c>
@@ -8501,7 +8502,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="12" t="s">
         <v>209</v>
       </c>
@@ -8535,7 +8536,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="12" t="s">
         <v>209</v>
       </c>
@@ -8567,7 +8568,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="12" t="s">
         <v>211</v>
       </c>
@@ -8597,7 +8598,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="12" t="s">
         <v>211</v>
       </c>
@@ -8631,7 +8632,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="12" t="s">
         <v>211</v>
       </c>
@@ -8663,7 +8664,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="12" t="s">
         <v>211</v>
       </c>
@@ -8695,7 +8696,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="12" t="s">
         <v>211</v>
       </c>
@@ -8729,7 +8730,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="12" t="s">
         <v>211</v>
       </c>
@@ -8763,7 +8764,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="12" t="s">
         <v>213</v>
       </c>
@@ -8793,7 +8794,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="12" t="s">
         <v>213</v>
       </c>
@@ -8827,7 +8828,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="12" t="s">
         <v>213</v>
       </c>
@@ -8861,7 +8862,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="12" t="s">
         <v>213</v>
       </c>
@@ -8893,7 +8894,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="12" t="s">
         <v>213</v>
       </c>
@@ -8927,7 +8928,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="12" t="s">
         <v>213</v>
       </c>
@@ -8959,7 +8960,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="12" t="s">
         <v>215</v>
       </c>
@@ -8993,7 +8994,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="12" t="s">
         <v>215</v>
       </c>
@@ -9029,7 +9030,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="12" t="s">
         <v>215</v>
       </c>
@@ -9061,7 +9062,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="12" t="s">
         <v>215</v>
       </c>
@@ -9095,7 +9096,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="12" t="s">
         <v>215</v>
       </c>
@@ -9127,7 +9128,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="12" t="s">
         <v>215</v>
       </c>
@@ -9159,7 +9160,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="12" t="s">
         <v>221</v>
       </c>
@@ -9193,7 +9194,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="12" t="s">
         <v>221</v>
       </c>
@@ -9229,7 +9230,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="12" t="s">
         <v>221</v>
       </c>
@@ -9263,7 +9264,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="12" t="s">
         <v>221</v>
       </c>
@@ -9297,7 +9298,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="12" t="s">
         <v>221</v>
       </c>
@@ -9327,7 +9328,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="12" t="s">
         <v>221</v>
       </c>
@@ -9359,7 +9360,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="12" t="s">
         <v>227</v>
       </c>
@@ -9393,7 +9394,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="12" t="s">
         <v>227</v>
       </c>
@@ -9427,7 +9428,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="12" t="s">
         <v>227</v>
       </c>
@@ -9459,7 +9460,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="12" t="s">
         <v>227</v>
       </c>
@@ -9493,7 +9494,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="12" t="s">
         <v>227</v>
       </c>
@@ -9525,7 +9526,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="12" t="s">
         <v>227</v>
       </c>
@@ -9559,7 +9560,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="12" t="s">
         <v>232</v>
       </c>
@@ -9593,7 +9594,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="12" t="s">
         <v>232</v>
       </c>
@@ -9627,7 +9628,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="12" t="s">
         <v>232</v>
       </c>
@@ -9661,7 +9662,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="12" t="s">
         <v>232</v>
       </c>
@@ -9695,7 +9696,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="12" t="s">
         <v>232</v>
       </c>
@@ -9727,7 +9728,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="12" t="s">
         <v>232</v>
       </c>
@@ -9759,7 +9760,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="12" t="s">
         <v>237</v>
       </c>
@@ -9791,7 +9792,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="12" t="s">
         <v>237</v>
       </c>
@@ -9825,7 +9826,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="12" t="s">
         <v>237</v>
       </c>
@@ -9855,7 +9856,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="12" t="s">
         <v>237</v>
       </c>
@@ -9889,7 +9890,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="12" t="s">
         <v>237</v>
       </c>
@@ -9923,7 +9924,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="12" t="s">
         <v>237</v>
       </c>
@@ -9955,7 +9956,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
         <v>242</v>
       </c>
@@ -9989,7 +9990,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243" s="9" t="s">
         <v>242</v>
       </c>
@@ -10021,7 +10022,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" s="9" t="s">
         <v>242</v>
       </c>
@@ -10053,7 +10054,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" s="9" t="s">
         <v>242</v>
       </c>
@@ -10085,7 +10086,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" s="9" t="s">
         <v>242</v>
       </c>
@@ -10119,7 +10120,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="12" t="s">
         <v>242</v>
       </c>
@@ -10153,7 +10154,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="12" t="s">
         <v>250</v>
       </c>
@@ -10181,7 +10182,7 @@
       <c r="K248" s="7"/>
       <c r="L248" s="8"/>
     </row>
-    <row r="249" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="12" t="s">
         <v>250</v>
       </c>
@@ -10209,7 +10210,7 @@
       <c r="K249" s="6"/>
       <c r="L249" s="11"/>
     </row>
-    <row r="250" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="12" t="s">
         <v>250</v>
       </c>
@@ -10237,7 +10238,7 @@
       <c r="K250" s="6"/>
       <c r="L250" s="11"/>
     </row>
-    <row r="251" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="12" t="s">
         <v>250</v>
       </c>
@@ -10265,7 +10266,7 @@
       </c>
       <c r="L251" s="11"/>
     </row>
-    <row r="252" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="12" t="s">
         <v>250</v>
       </c>
@@ -10293,7 +10294,7 @@
       <c r="K252" s="6"/>
       <c r="L252" s="11"/>
     </row>
-    <row r="253" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="12" t="s">
         <v>250</v>
       </c>
@@ -10321,7 +10322,7 @@
       </c>
       <c r="L253" s="15"/>
     </row>
-    <row r="254" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="12" t="s">
         <v>256</v>
       </c>
@@ -10351,7 +10352,7 @@
       </c>
       <c r="L254" s="8"/>
     </row>
-    <row r="255" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="12" t="s">
         <v>256</v>
       </c>
@@ -10377,7 +10378,7 @@
       <c r="K255" s="6"/>
       <c r="L255" s="11"/>
     </row>
-    <row r="256" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="12" t="s">
         <v>256</v>
       </c>
@@ -10405,7 +10406,7 @@
       </c>
       <c r="L256" s="11"/>
     </row>
-    <row r="257" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="12" t="s">
         <v>256</v>
       </c>
@@ -10435,7 +10436,7 @@
       </c>
       <c r="L257" s="11"/>
     </row>
-    <row r="258" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="12" t="s">
         <v>256</v>
       </c>
@@ -10461,7 +10462,7 @@
       <c r="K258" s="6"/>
       <c r="L258" s="11"/>
     </row>
-    <row r="259" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="12" t="s">
         <v>256</v>
       </c>
@@ -10487,7 +10488,7 @@
       </c>
       <c r="L259" s="15"/>
     </row>
-    <row r="260" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="12" t="s">
         <v>258</v>
       </c>
@@ -10519,7 +10520,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="261" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="12" t="s">
         <v>258</v>
       </c>
@@ -10553,7 +10554,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="12" t="s">
         <v>258</v>
       </c>
@@ -10587,7 +10588,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="12" t="s">
         <v>258</v>
       </c>
@@ -10619,7 +10620,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="12" t="s">
         <v>258</v>
       </c>
@@ -10653,7 +10654,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="12" t="s">
         <v>258</v>
       </c>
@@ -10685,7 +10686,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="266" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="12" t="s">
         <v>262</v>
       </c>
@@ -10713,7 +10714,7 @@
       </c>
       <c r="L266" s="8"/>
     </row>
-    <row r="267" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="12" t="s">
         <v>262</v>
       </c>
@@ -10743,7 +10744,7 @@
       <c r="K267" s="6"/>
       <c r="L267" s="11"/>
     </row>
-    <row r="268" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="12" t="s">
         <v>262</v>
       </c>
@@ -10771,7 +10772,7 @@
       <c r="K268" s="6"/>
       <c r="L268" s="11"/>
     </row>
-    <row r="269" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="12" t="s">
         <v>262</v>
       </c>
@@ -10801,7 +10802,7 @@
       </c>
       <c r="L269" s="11"/>
     </row>
-    <row r="270" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="12" t="s">
         <v>262</v>
       </c>
@@ -10831,7 +10832,7 @@
       </c>
       <c r="L270" s="11"/>
     </row>
-    <row r="271" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="12" t="s">
         <v>262</v>
       </c>
@@ -10861,7 +10862,7 @@
       </c>
       <c r="L271" s="15"/>
     </row>
-    <row r="272" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="12" t="s">
         <v>273</v>
       </c>
@@ -10889,7 +10890,7 @@
       </c>
       <c r="L272" s="8"/>
     </row>
-    <row r="273" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="12" t="s">
         <v>273</v>
       </c>
@@ -10921,7 +10922,7 @@
       <c r="K273" s="6"/>
       <c r="L273" s="11"/>
     </row>
-    <row r="274" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="12" t="s">
         <v>273</v>
       </c>
@@ -10951,7 +10952,7 @@
       <c r="K274" s="6"/>
       <c r="L274" s="11"/>
     </row>
-    <row r="275" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="12" t="s">
         <v>273</v>
       </c>
@@ -10981,7 +10982,7 @@
       <c r="K275" s="6"/>
       <c r="L275" s="11"/>
     </row>
-    <row r="276" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="12" t="s">
         <v>273</v>
       </c>
@@ -11007,7 +11008,7 @@
       <c r="K276" s="6"/>
       <c r="L276" s="11"/>
     </row>
-    <row r="277" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="12" t="s">
         <v>273</v>
       </c>
@@ -11035,7 +11036,7 @@
       <c r="K277" s="14"/>
       <c r="L277" s="15"/>
     </row>
-    <row r="278" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="12" t="s">
         <v>284</v>
       </c>
@@ -11067,7 +11068,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="279" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="12" t="s">
         <v>284</v>
       </c>
@@ -11099,7 +11100,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="280" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="12" t="s">
         <v>284</v>
       </c>
@@ -11131,7 +11132,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="12" t="s">
         <v>284</v>
       </c>
@@ -11163,7 +11164,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="282" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="12" t="s">
         <v>284</v>
       </c>
@@ -11197,7 +11198,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="283" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="12" t="s">
         <v>284</v>
       </c>
@@ -11231,7 +11232,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="284" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="12" t="s">
         <v>291</v>
       </c>
@@ -11263,7 +11264,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="285" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="12" t="s">
         <v>291</v>
       </c>
@@ -11297,7 +11298,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="12" t="s">
         <v>291</v>
       </c>
@@ -11329,7 +11330,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="287" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="12" t="s">
         <v>291</v>
       </c>
@@ -11363,7 +11364,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="12" t="s">
         <v>291</v>
       </c>
@@ -11397,7 +11398,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="289" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="12" t="s">
         <v>291</v>
       </c>
@@ -11431,7 +11432,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="290" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="12" t="s">
         <v>301</v>
       </c>
@@ -11461,7 +11462,7 @@
       </c>
       <c r="L290" s="8"/>
     </row>
-    <row r="291" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="12" t="s">
         <v>301</v>
       </c>
@@ -11491,7 +11492,7 @@
       </c>
       <c r="L291" s="11"/>
     </row>
-    <row r="292" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="12" t="s">
         <v>301</v>
       </c>
@@ -11519,7 +11520,7 @@
       </c>
       <c r="L292" s="11"/>
     </row>
-    <row r="293" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="12" t="s">
         <v>301</v>
       </c>
@@ -11547,7 +11548,7 @@
       <c r="K293" s="6"/>
       <c r="L293" s="11"/>
     </row>
-    <row r="294" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="12" t="s">
         <v>301</v>
       </c>
@@ -11577,7 +11578,7 @@
       <c r="K294" s="6"/>
       <c r="L294" s="11"/>
     </row>
-    <row r="295" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="12" t="s">
         <v>301</v>
       </c>
@@ -11607,7 +11608,7 @@
       </c>
       <c r="L295" s="15"/>
     </row>
-    <row r="296" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="12" t="s">
         <v>303</v>
       </c>
@@ -11641,7 +11642,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="12" t="s">
         <v>303</v>
       </c>
@@ -11675,7 +11676,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="12" t="s">
         <v>303</v>
       </c>
@@ -11709,7 +11710,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="299" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="12" t="s">
         <v>303</v>
       </c>
@@ -11741,7 +11742,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="300" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="12" t="s">
         <v>303</v>
       </c>
@@ -11775,7 +11776,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="301" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="12" t="s">
         <v>303</v>
       </c>
@@ -11809,7 +11810,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="302" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="12" t="s">
         <v>305</v>
       </c>
@@ -11837,7 +11838,7 @@
       <c r="K302" s="7"/>
       <c r="L302" s="8"/>
     </row>
-    <row r="303" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="12" t="s">
         <v>305</v>
       </c>
@@ -11867,7 +11868,7 @@
       </c>
       <c r="L303" s="11"/>
     </row>
-    <row r="304" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="12" t="s">
         <v>305</v>
       </c>
@@ -11897,7 +11898,7 @@
       </c>
       <c r="L304" s="11"/>
     </row>
-    <row r="305" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="12" t="s">
         <v>305</v>
       </c>
@@ -11927,7 +11928,7 @@
       </c>
       <c r="L305" s="11"/>
     </row>
-    <row r="306" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="12" t="s">
         <v>305</v>
       </c>
@@ -11957,7 +11958,7 @@
       </c>
       <c r="L306" s="11"/>
     </row>
-    <row r="307" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="12" t="s">
         <v>305</v>
       </c>
@@ -11987,7 +11988,7 @@
       </c>
       <c r="L307" s="15"/>
     </row>
-    <row r="308" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="12" t="s">
         <v>306</v>
       </c>
@@ -12021,7 +12022,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="309" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="12" t="s">
         <v>306</v>
       </c>
@@ -12053,7 +12054,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="310" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="12" t="s">
         <v>306</v>
       </c>
@@ -12083,7 +12084,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="311" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="12" t="s">
         <v>306</v>
       </c>
@@ -12113,7 +12114,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="312" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="12" t="s">
         <v>306</v>
       </c>
@@ -12145,7 +12146,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="313" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="12" t="s">
         <v>306</v>
       </c>
@@ -12179,7 +12180,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="314" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="12" t="s">
         <v>308</v>
       </c>
@@ -12211,7 +12212,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="315" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="12" t="s">
         <v>308</v>
       </c>
@@ -12245,7 +12246,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="316" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="12" t="s">
         <v>308</v>
       </c>
@@ -12277,7 +12278,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="317" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="12" t="s">
         <v>308</v>
       </c>
@@ -12309,7 +12310,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="318" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="12" t="s">
         <v>308</v>
       </c>
@@ -12339,7 +12340,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="319" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="12" t="s">
         <v>308</v>
       </c>
@@ -12371,7 +12372,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="320" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="12" t="s">
         <v>310</v>
       </c>
@@ -12399,7 +12400,7 @@
       <c r="K320" s="7"/>
       <c r="L320" s="8"/>
     </row>
-    <row r="321" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="12" t="s">
         <v>310</v>
       </c>
@@ -12429,7 +12430,7 @@
       </c>
       <c r="L321" s="11"/>
     </row>
-    <row r="322" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="12" t="s">
         <v>310</v>
       </c>
@@ -12457,7 +12458,7 @@
       </c>
       <c r="L322" s="11"/>
     </row>
-    <row r="323" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="12" t="s">
         <v>310</v>
       </c>
@@ -12485,7 +12486,7 @@
       <c r="K323" s="6"/>
       <c r="L323" s="11"/>
     </row>
-    <row r="324" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="12" t="s">
         <v>310</v>
       </c>
@@ -12513,7 +12514,7 @@
       <c r="K324" s="6"/>
       <c r="L324" s="11"/>
     </row>
-    <row r="325" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="12" t="s">
         <v>310</v>
       </c>
@@ -12541,7 +12542,7 @@
       <c r="K325" s="14"/>
       <c r="L325" s="15"/>
     </row>
-    <row r="326" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="12" t="s">
         <v>314</v>
       </c>
@@ -12569,7 +12570,7 @@
       </c>
       <c r="L326" s="8"/>
     </row>
-    <row r="327" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="12" t="s">
         <v>314</v>
       </c>
@@ -12597,7 +12598,7 @@
       <c r="K327" s="6"/>
       <c r="L327" s="11"/>
     </row>
-    <row r="328" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="12" t="s">
         <v>314</v>
       </c>
@@ -12625,7 +12626,7 @@
       <c r="K328" s="6"/>
       <c r="L328" s="11"/>
     </row>
-    <row r="329" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="12" t="s">
         <v>314</v>
       </c>
@@ -12653,7 +12654,7 @@
       </c>
       <c r="L329" s="11"/>
     </row>
-    <row r="330" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="12" t="s">
         <v>314</v>
       </c>
@@ -12681,7 +12682,7 @@
       <c r="K330" s="6"/>
       <c r="L330" s="11"/>
     </row>
-    <row r="331" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="12" t="s">
         <v>314</v>
       </c>
@@ -12709,7 +12710,7 @@
       </c>
       <c r="L331" s="15"/>
     </row>
-    <row r="332" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="12" t="s">
         <v>321</v>
       </c>
@@ -12741,7 +12742,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="333" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="12" t="s">
         <v>321</v>
       </c>
@@ -12775,7 +12776,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="334" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="12" t="s">
         <v>321</v>
       </c>
@@ -12807,7 +12808,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="335" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="12" t="s">
         <v>321</v>
       </c>
@@ -12841,7 +12842,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="336" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="12" t="s">
         <v>321</v>
       </c>
@@ -12873,7 +12874,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="337" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="12" t="s">
         <v>321</v>
       </c>
@@ -12906,7 +12907,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="338" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="12" t="s">
         <v>330</v>
       </c>
@@ -12936,7 +12937,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="339" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="12" t="s">
         <v>330</v>
       </c>
@@ -12968,7 +12969,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="340" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="12" t="s">
         <v>330</v>
       </c>
@@ -13000,7 +13001,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="341" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="12" t="s">
         <v>330</v>
       </c>
@@ -13034,7 +13035,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="342" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="12" t="s">
         <v>330</v>
       </c>
@@ -13068,7 +13069,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="343" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="12" t="s">
         <v>330</v>
       </c>
@@ -13100,7 +13101,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="344" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="12" t="s">
         <v>339</v>
       </c>
@@ -13132,7 +13133,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="345" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="12" t="s">
         <v>339</v>
       </c>
@@ -13164,7 +13165,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="346" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="12" t="s">
         <v>339</v>
       </c>
@@ -13198,7 +13199,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="347" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="12" t="s">
         <v>339</v>
       </c>
@@ -13230,7 +13231,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="348" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="12" t="s">
         <v>339</v>
       </c>
@@ -13262,7 +13263,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="349" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="12" t="s">
         <v>339</v>
       </c>
@@ -13294,7 +13295,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="350" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="12" t="s">
         <v>349</v>
       </c>
@@ -13326,7 +13327,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="351" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="12" t="s">
         <v>349</v>
       </c>
@@ -13358,7 +13359,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="352" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="12" t="s">
         <v>349</v>
       </c>
@@ -13392,7 +13393,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="353" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="12" t="s">
         <v>349</v>
       </c>
@@ -13424,7 +13425,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="354" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="12" t="s">
         <v>349</v>
       </c>
@@ -13458,7 +13459,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="355" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="12" t="s">
         <v>349</v>
       </c>
@@ -13490,7 +13491,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="356" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="12" t="s">
         <v>358</v>
       </c>
@@ -13524,7 +13525,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="357" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="12" t="s">
         <v>358</v>
       </c>
@@ -13556,7 +13557,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="358" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="12" t="s">
         <v>358</v>
       </c>
@@ -13588,7 +13589,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="359" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="12" t="s">
         <v>358</v>
       </c>
@@ -13622,7 +13623,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="360" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="12" t="s">
         <v>358</v>
       </c>
@@ -13656,7 +13657,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="361" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="12" t="s">
         <v>358</v>
       </c>
@@ -13688,7 +13689,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="362" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="12" t="s">
         <v>367</v>
       </c>
@@ -13722,7 +13723,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="363" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="12" t="s">
         <v>367</v>
       </c>
@@ -13752,7 +13753,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="364" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="12" t="s">
         <v>367</v>
       </c>
@@ -13786,7 +13787,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="365" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="12" t="s">
         <v>367</v>
       </c>
@@ -13816,7 +13817,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="366" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="12" t="s">
         <v>367</v>
       </c>
@@ -13850,7 +13851,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="367" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="12" t="s">
         <v>367</v>
       </c>
@@ -13882,7 +13883,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="368" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="12" t="s">
         <v>378</v>
       </c>
@@ -13912,7 +13913,7 @@
       </c>
       <c r="L368" s="8"/>
     </row>
-    <row r="369" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="12" t="s">
         <v>378</v>
       </c>
@@ -13942,7 +13943,7 @@
       </c>
       <c r="L369" s="11"/>
     </row>
-    <row r="370" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="12" t="s">
         <v>378</v>
       </c>
@@ -13970,7 +13971,7 @@
       </c>
       <c r="L370" s="11"/>
     </row>
-    <row r="371" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="12" t="s">
         <v>378</v>
       </c>
@@ -13996,7 +13997,7 @@
       <c r="K371" s="6"/>
       <c r="L371" s="11"/>
     </row>
-    <row r="372" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="12" t="s">
         <v>378</v>
       </c>
@@ -14026,7 +14027,7 @@
       </c>
       <c r="L372" s="11"/>
     </row>
-    <row r="373" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="12" t="s">
         <v>378</v>
       </c>
@@ -14054,7 +14055,7 @@
       </c>
       <c r="L373" s="15"/>
     </row>
-    <row r="374" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="12" t="s">
         <v>391</v>
       </c>
@@ -14082,7 +14083,7 @@
       <c r="K374" s="7"/>
       <c r="L374" s="8"/>
     </row>
-    <row r="375" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="12" t="s">
         <v>391</v>
       </c>
@@ -14110,7 +14111,7 @@
       <c r="K375" s="6"/>
       <c r="L375" s="11"/>
     </row>
-    <row r="376" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="12" t="s">
         <v>391</v>
       </c>
@@ -14138,7 +14139,7 @@
       <c r="K376" s="6"/>
       <c r="L376" s="11"/>
     </row>
-    <row r="377" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="12" t="s">
         <v>391</v>
       </c>
@@ -14170,7 +14171,7 @@
       </c>
       <c r="L377" s="11"/>
     </row>
-    <row r="378" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="12" t="s">
         <v>391</v>
       </c>
@@ -14200,7 +14201,7 @@
       <c r="K378" s="6"/>
       <c r="L378" s="11"/>
     </row>
-    <row r="379" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="12" t="s">
         <v>391</v>
       </c>
@@ -14230,7 +14231,7 @@
       <c r="K379" s="14"/>
       <c r="L379" s="15"/>
     </row>
-    <row r="380" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="12" t="s">
         <v>396</v>
       </c>
@@ -14258,7 +14259,7 @@
       </c>
       <c r="L380" s="8"/>
     </row>
-    <row r="381" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="12" t="s">
         <v>396</v>
       </c>
@@ -14286,7 +14287,7 @@
       </c>
       <c r="L381" s="11"/>
     </row>
-    <row r="382" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="12" t="s">
         <v>396</v>
       </c>
@@ -14316,7 +14317,7 @@
       </c>
       <c r="L382" s="11"/>
     </row>
-    <row r="383" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="12" t="s">
         <v>396</v>
       </c>
@@ -14346,7 +14347,7 @@
       </c>
       <c r="L383" s="11"/>
     </row>
-    <row r="384" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="12" t="s">
         <v>396</v>
       </c>
@@ -14374,7 +14375,7 @@
       </c>
       <c r="L384" s="11"/>
     </row>
-    <row r="385" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="12" t="s">
         <v>396</v>
       </c>
@@ -14402,7 +14403,7 @@
       </c>
       <c r="L385" s="15"/>
     </row>
-    <row r="386" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="12" t="s">
         <v>398</v>
       </c>
@@ -14432,7 +14433,7 @@
       </c>
       <c r="L386" s="8"/>
     </row>
-    <row r="387" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="12" t="s">
         <v>398</v>
       </c>
@@ -14462,7 +14463,7 @@
       </c>
       <c r="L387" s="11"/>
     </row>
-    <row r="388" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="12" t="s">
         <v>398</v>
       </c>
@@ -14492,7 +14493,7 @@
       </c>
       <c r="L388" s="11"/>
     </row>
-    <row r="389" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="12" t="s">
         <v>398</v>
       </c>
@@ -14516,7 +14517,7 @@
       </c>
       <c r="L389" s="11"/>
     </row>
-    <row r="390" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="12" t="s">
         <v>398</v>
       </c>
@@ -14542,7 +14543,7 @@
       </c>
       <c r="L390" s="11"/>
     </row>
-    <row r="391" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="12" t="s">
         <v>398</v>
       </c>
@@ -14570,7 +14571,7 @@
       </c>
       <c r="L391" s="15"/>
     </row>
-    <row r="392" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="12" t="s">
         <v>407</v>
       </c>
@@ -14596,7 +14597,7 @@
       <c r="K392" s="7"/>
       <c r="L392" s="8"/>
     </row>
-    <row r="393" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="12" t="s">
         <v>407</v>
       </c>
@@ -14622,7 +14623,7 @@
       <c r="K393" s="6"/>
       <c r="L393" s="11"/>
     </row>
-    <row r="394" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="12" t="s">
         <v>407</v>
       </c>
@@ -14648,7 +14649,7 @@
       </c>
       <c r="L394" s="11"/>
     </row>
-    <row r="395" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="12" t="s">
         <v>407</v>
       </c>
@@ -14678,7 +14679,7 @@
       </c>
       <c r="L395" s="11"/>
     </row>
-    <row r="396" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="12" t="s">
         <v>407</v>
       </c>
@@ -14708,7 +14709,7 @@
       </c>
       <c r="L396" s="11"/>
     </row>
-    <row r="397" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="12" t="s">
         <v>407</v>
       </c>
@@ -14738,7 +14739,7 @@
       </c>
       <c r="L397" s="15"/>
     </row>
-    <row r="398" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="12" t="s">
         <v>412</v>
       </c>
@@ -14768,7 +14769,7 @@
       </c>
       <c r="L398" s="8"/>
     </row>
-    <row r="399" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="12" t="s">
         <v>412</v>
       </c>
@@ -14796,7 +14797,7 @@
       </c>
       <c r="L399" s="11"/>
     </row>
-    <row r="400" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="12" t="s">
         <v>412</v>
       </c>
@@ -14807,6 +14808,7 @@
       <c r="D400" s="6" t="s">
         <v>417</v>
       </c>
+      <c r="E400" s="6"/>
       <c r="F400" s="6" t="s">
         <v>414</v>
       </c>
@@ -14821,7 +14823,7 @@
       </c>
       <c r="L400" s="11"/>
     </row>
-    <row r="401" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="12" t="s">
         <v>412</v>
       </c>
@@ -14847,11 +14849,11 @@
         <v>418</v>
       </c>
       <c r="K401" s="6" t="s">
-        <v>535</v>
+        <v>422</v>
       </c>
       <c r="L401" s="11"/>
     </row>
-    <row r="402" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="12" t="s">
         <v>412</v>
       </c>
@@ -14881,7 +14883,7 @@
       <c r="K402" s="6"/>
       <c r="L402" s="11"/>
     </row>
-    <row r="403" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="12" t="s">
         <v>412</v>
       </c>
@@ -14907,9 +14909,9 @@
       </c>
       <c r="L403" s="15"/>
     </row>
-    <row r="404" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B404" s="5" t="s">
         <v>13</v>
@@ -14927,9 +14929,9 @@
       <c r="K404" s="7"/>
       <c r="L404" s="8"/>
     </row>
-    <row r="405" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B405" s="10" t="s">
         <v>16</v>
@@ -14947,9 +14949,9 @@
       <c r="K405" s="6"/>
       <c r="L405" s="11"/>
     </row>
-    <row r="406" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B406" s="10" t="s">
         <v>20</v>
@@ -14969,9 +14971,9 @@
       <c r="K406" s="6"/>
       <c r="L406" s="11"/>
     </row>
-    <row r="407" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B407" s="10" t="s">
         <v>22</v>
@@ -14991,9 +14993,9 @@
       <c r="K407" s="6"/>
       <c r="L407" s="11"/>
     </row>
-    <row r="408" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A408" s="12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B408" s="10" t="s">
         <v>25</v>
@@ -15011,9 +15013,9 @@
       <c r="K408" s="6"/>
       <c r="L408" s="11"/>
     </row>
-    <row r="409" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A409" s="12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B409" s="13" t="s">
         <v>27</v>
@@ -15031,15 +15033,15 @@
       <c r="K409" s="14"/>
       <c r="L409" s="15"/>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A410" s="19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B410" s="20" t="s">
         <v>13</v>
       </c>
       <c r="C410" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D410" s="18" t="s">
         <v>60</v>
@@ -15055,25 +15057,25 @@
         <v>312</v>
       </c>
       <c r="I410" s="18" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J410" s="18" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K410" s="18"/>
       <c r="L410" s="18" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A411" s="19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B411" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C411" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D411" s="6" t="s">
         <v>60</v>
@@ -15090,7 +15092,7 @@
       </c>
       <c r="I411" s="6"/>
       <c r="J411" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K411" s="6" t="s">
         <v>312</v>
@@ -15099,15 +15101,15 @@
         <v>73</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A412" s="19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B412" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C412" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D412" s="6" t="s">
         <v>60</v>
@@ -15121,25 +15123,25 @@
         <v>312</v>
       </c>
       <c r="I412" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J412" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K412" s="6"/>
       <c r="L412" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A413" s="19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B413" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C413" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D413" s="6" t="s">
         <v>60</v>
@@ -15156,22 +15158,22 @@
         <v>312</v>
       </c>
       <c r="J413" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K413" s="6"/>
       <c r="L413" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A414" s="19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B414" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C414" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D414" s="6" t="s">
         <v>60</v>
@@ -15188,22 +15190,22 @@
         <v>60</v>
       </c>
       <c r="J414" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K414" s="6"/>
       <c r="L414" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="415" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A415" s="19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B415" s="19" t="s">
         <v>27</v>
       </c>
       <c r="C415" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D415" s="21" t="s">
         <v>60</v>
@@ -15220,16 +15222,16 @@
         <v>60</v>
       </c>
       <c r="J415" s="21" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K415" s="21"/>
       <c r="L415" s="21" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="416" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A416" s="12" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B416" s="5" t="s">
         <v>13</v>
@@ -15237,13 +15239,13 @@
       <c r="C416" s="6"/>
       <c r="D416" s="7"/>
       <c r="E416" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F416" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G416" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H416" s="7"/>
       <c r="I416" s="7"/>
@@ -15253,9 +15255,9 @@
       <c r="K416" s="7"/>
       <c r="L416" s="8"/>
     </row>
-    <row r="417" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A417" s="12" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B417" s="10" t="s">
         <v>16</v>
@@ -15263,41 +15265,41 @@
       <c r="C417" s="6"/>
       <c r="D417" s="6"/>
       <c r="E417" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F417" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G417" s="6"/>
       <c r="H417" s="6"/>
       <c r="I417" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J417" s="6" t="s">
         <v>393</v>
       </c>
       <c r="K417" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="L417" s="11"/>
+    </row>
+    <row r="418" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A418" s="12" t="s">
         <v>427</v>
-      </c>
-      <c r="L417" s="11"/>
-    </row>
-    <row r="418" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A418" s="12" t="s">
-        <v>426</v>
       </c>
       <c r="B418" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C418" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D418" s="6"/>
       <c r="E418" s="6"/>
       <c r="F418" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G418" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H418" s="6"/>
       <c r="I418" s="6"/>
@@ -15305,27 +15307,27 @@
         <v>393</v>
       </c>
       <c r="K418" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="L418" s="11"/>
+    </row>
+    <row r="419" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A419" s="12" t="s">
         <v>427</v>
-      </c>
-      <c r="L418" s="11"/>
-    </row>
-    <row r="419" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A419" s="12" t="s">
-        <v>426</v>
       </c>
       <c r="B419" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C419" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D419" s="6"/>
       <c r="E419" s="6"/>
       <c r="F419" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G419" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H419" s="6"/>
       <c r="I419" s="6" t="s">
@@ -15337,9 +15339,9 @@
       <c r="K419" s="6"/>
       <c r="L419" s="11"/>
     </row>
-    <row r="420" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A420" s="12" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B420" s="10" t="s">
         <v>25</v>
@@ -15348,10 +15350,10 @@
       <c r="D420" s="6"/>
       <c r="E420" s="6"/>
       <c r="F420" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G420" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H420" s="6"/>
       <c r="I420" s="6" t="s">
@@ -15363,9 +15365,9 @@
       <c r="K420" s="6"/>
       <c r="L420" s="11"/>
     </row>
-    <row r="421" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A421" s="12" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B421" s="13" t="s">
         <v>27</v>
@@ -15373,13 +15375,13 @@
       <c r="C421" s="14"/>
       <c r="D421" s="14"/>
       <c r="E421" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="F421" s="14" t="s">
         <v>428</v>
       </c>
-      <c r="F421" s="14" t="s">
-        <v>427</v>
-      </c>
       <c r="G421" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H421" s="14"/>
       <c r="I421" s="14" t="s">
@@ -15391,31 +15393,31 @@
       <c r="K421" s="14"/>
       <c r="L421" s="15"/>
     </row>
-    <row r="422" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A422" s="12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B422" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C422" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D422" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E422" s="7"/>
       <c r="F422" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G422" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H422" s="7" t="s">
         <v>408</v>
       </c>
       <c r="I422" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J422" s="7" t="s">
         <v>393</v>
@@ -15425,29 +15427,29 @@
         <v>46</v>
       </c>
     </row>
-    <row r="423" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A423" s="12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B423" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D423" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E423" s="6"/>
       <c r="F423" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G423" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H423" s="6"/>
       <c r="I423" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J423" s="6" t="s">
         <v>393</v>
@@ -15457,26 +15459,26 @@
         <v>46</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A424" s="12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B424" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C424" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D424" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E424" s="6"/>
       <c r="F424" s="6"/>
       <c r="G424" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H424" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I424" s="6"/>
       <c r="J424" s="6" t="s">
@@ -15487,27 +15489,27 @@
         <v>46</v>
       </c>
     </row>
-    <row r="425" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A425" s="12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B425" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C425" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D425" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E425" s="6"/>
       <c r="F425" s="6"/>
       <c r="G425" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H425" s="6"/>
       <c r="I425" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J425" s="6" t="s">
         <v>393</v>
@@ -15517,27 +15519,27 @@
         <v>46</v>
       </c>
     </row>
-    <row r="426" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A426" s="12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B426" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C426" s="6"/>
       <c r="D426" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E426" s="6" t="s">
         <v>408</v>
       </c>
       <c r="F426" s="6"/>
       <c r="G426" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H426" s="6"/>
       <c r="I426" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J426" s="6" t="s">
         <v>393</v>
@@ -15547,23 +15549,23 @@
         <v>46</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A427" s="12" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B427" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C427" s="14"/>
       <c r="D427" s="14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E427" s="14" t="s">
         <v>408</v>
       </c>
       <c r="F427" s="14"/>
       <c r="G427" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H427" s="14"/>
       <c r="I427" s="14"/>
@@ -15575,9 +15577,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A428" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B428" s="5" t="s">
         <v>13</v>
@@ -15588,24 +15590,24 @@
         <v>399</v>
       </c>
       <c r="F428" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G428" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H428" s="7"/>
       <c r="I428" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J428" s="7" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="8"/>
     </row>
-    <row r="429" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A429" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B429" s="10" t="s">
         <v>16</v>
@@ -15616,22 +15618,22 @@
         <v>399</v>
       </c>
       <c r="F429" s="6" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G429" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H429" s="6"/>
       <c r="I429" s="6"/>
       <c r="J429" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K429" s="6"/>
       <c r="L429" s="11"/>
     </row>
-    <row r="430" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A430" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B430" s="10" t="s">
         <v>20</v>
@@ -15642,24 +15644,24 @@
         <v>399</v>
       </c>
       <c r="F430" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G430" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H430" s="6"/>
       <c r="I430" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J430" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K430" s="6"/>
       <c r="L430" s="11"/>
     </row>
-    <row r="431" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A431" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B431" s="10" t="s">
         <v>22</v>
@@ -15668,24 +15670,24 @@
       <c r="D431" s="6"/>
       <c r="E431" s="6"/>
       <c r="F431" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G431" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H431" s="6"/>
       <c r="I431" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J431" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K431" s="6"/>
       <c r="L431" s="11"/>
     </row>
-    <row r="432" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A432" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B432" s="10" t="s">
         <v>25</v>
@@ -15694,24 +15696,24 @@
       <c r="D432" s="6"/>
       <c r="E432" s="6"/>
       <c r="F432" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G432" s="6" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H432" s="6"/>
       <c r="I432" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J432" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K432" s="6"/>
       <c r="L432" s="11"/>
     </row>
-    <row r="433" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A433" s="12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B433" s="13" t="s">
         <v>27</v>
@@ -15721,21 +15723,21 @@
       <c r="E433" s="14"/>
       <c r="F433" s="14"/>
       <c r="G433" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H433" s="14"/>
       <c r="I433" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J433" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K433" s="14"/>
       <c r="L433" s="15"/>
     </row>
-    <row r="434" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A434" s="12" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B434" s="5" t="s">
         <v>13</v>
@@ -15744,28 +15746,28 @@
         <v>274</v>
       </c>
       <c r="D434" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E434" s="7"/>
       <c r="F434" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G434" s="7"/>
       <c r="H434" s="7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I434" s="7"/>
       <c r="J434" s="7" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="435" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A435" s="12" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B435" s="10" t="s">
         <v>16</v>
@@ -15774,218 +15776,218 @@
         <v>277</v>
       </c>
       <c r="D435" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E435" s="6"/>
       <c r="F435" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G435" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="H435" s="6" t="s">
         <v>445</v>
-      </c>
-      <c r="H435" s="6" t="s">
-        <v>444</v>
       </c>
       <c r="I435" s="6"/>
       <c r="J435" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="K435" s="6" t="s">
         <v>445</v>
-      </c>
-      <c r="K435" s="6" t="s">
-        <v>444</v>
       </c>
       <c r="L435" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="436" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A436" s="12" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B436" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C436" s="6" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D436" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E436" s="6"/>
       <c r="F436" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G436" s="6"/>
       <c r="H436" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I436" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J436" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K436" s="6"/>
       <c r="L436" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="437" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A437" s="12" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B437" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C437" s="6" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D437" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E437" s="6"/>
       <c r="F437" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G437" s="6"/>
       <c r="H437" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I437" s="6" t="s">
         <v>312</v>
       </c>
       <c r="J437" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K437" s="6"/>
       <c r="L437" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="438" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A438" s="12" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B438" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C438" s="6"/>
       <c r="D438" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E438" s="6"/>
       <c r="F438" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G438" s="6"/>
       <c r="H438" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I438" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J438" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K438" s="6"/>
       <c r="L438" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="439" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A439" s="12" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B439" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C439" s="14"/>
       <c r="D439" s="14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E439" s="14"/>
       <c r="F439" s="14"/>
       <c r="G439" s="14" t="s">
+        <v>444</v>
+      </c>
+      <c r="H439" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="I439" s="14" t="s">
         <v>443</v>
       </c>
-      <c r="H439" s="14" t="s">
-        <v>444</v>
-      </c>
-      <c r="I439" s="14" t="s">
-        <v>442</v>
-      </c>
       <c r="J439" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K439" s="14"/>
       <c r="L439" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="440" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A440" s="12" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B440" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C440" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D440" s="7"/>
       <c r="E440" s="7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F440" s="7"/>
       <c r="G440" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H440" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I440" s="7"/>
       <c r="J440" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K440" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L440" s="8" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="441" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A441" s="12" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B441" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C441" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D441" s="6"/>
       <c r="E441" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F441" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G441" s="6"/>
       <c r="H441" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I441" s="6"/>
       <c r="J441" s="6"/>
       <c r="K441" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L441" s="11" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="442" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A442" s="12" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B442" s="10" t="s">
         <v>20</v>
@@ -15994,20 +15996,20 @@
         <v>61</v>
       </c>
       <c r="D442" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="E442" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="E442" s="6" t="s">
-        <v>449</v>
-      </c>
       <c r="F442" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G442" s="6"/>
       <c r="H442" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I442" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J442" s="6"/>
       <c r="K442" s="6" t="s">
@@ -16017,31 +16019,31 @@
         <v>127</v>
       </c>
     </row>
-    <row r="443" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A443" s="12" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B443" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D443" s="6"/>
       <c r="E443" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F443" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G443" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H443" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I443" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J443" s="6"/>
       <c r="K443" s="6" t="s">
@@ -16051,9 +16053,9 @@
         <v>127</v>
       </c>
     </row>
-    <row r="444" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A444" s="12" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B444" s="10" t="s">
         <v>25</v>
@@ -16062,17 +16064,17 @@
         <v>397</v>
       </c>
       <c r="D444" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="E444" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="F444" s="6" t="s">
         <v>450</v>
-      </c>
-      <c r="E444" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="F444" s="6" t="s">
-        <v>449</v>
       </c>
       <c r="G444" s="6"/>
       <c r="H444" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I444" s="6"/>
       <c r="J444" s="6"/>
@@ -16083,9 +16085,9 @@
         <v>127</v>
       </c>
     </row>
-    <row r="445" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A445" s="12" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B445" s="13" t="s">
         <v>27</v>
@@ -16095,15 +16097,15 @@
       </c>
       <c r="D445" s="14"/>
       <c r="E445" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F445" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G445" s="14"/>
       <c r="H445" s="14"/>
       <c r="I445" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J445" s="14"/>
       <c r="K445" s="14" t="s">
@@ -16113,21 +16115,21 @@
         <v>127</v>
       </c>
     </row>
-    <row r="446" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A446" s="12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B446" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C446" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D446" s="7" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E446" s="7" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F446" s="7" t="s">
         <v>404</v>
@@ -16135,31 +16137,31 @@
       <c r="G446" s="7"/>
       <c r="H446" s="7"/>
       <c r="I446" s="7" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J446" s="7"/>
       <c r="K446" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L446" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="447" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A447" s="12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B447" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C447" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D447" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E447" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F447" s="6" t="s">
         <v>404</v>
@@ -16167,7 +16169,7 @@
       <c r="G447" s="6"/>
       <c r="H447" s="6"/>
       <c r="I447" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J447" s="6"/>
       <c r="K447" s="6" t="s">
@@ -16177,59 +16179,59 @@
         <v>55</v>
       </c>
     </row>
-    <row r="448" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A448" s="12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B448" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C448" s="6"/>
       <c r="D448" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E448" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F448" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G448" s="6"/>
       <c r="H448" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="I448" s="6" t="s">
         <v>459</v>
-      </c>
-      <c r="I448" s="6" t="s">
-        <v>458</v>
       </c>
       <c r="J448" s="6"/>
       <c r="K448" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L448" s="11" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="449" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A449" s="12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B449" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C449" s="6"/>
       <c r="D449" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E449" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F449" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G449" s="6"/>
       <c r="H449" s="6"/>
       <c r="I449" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J449" s="6"/>
       <c r="K449" s="6" t="s">
@@ -16239,27 +16241,27 @@
         <v>55</v>
       </c>
     </row>
-    <row r="450" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A450" s="12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B450" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C450" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D450" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E450" s="6"/>
       <c r="F450" s="6" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G450" s="6"/>
       <c r="H450" s="6"/>
       <c r="I450" s="6" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J450" s="6"/>
       <c r="K450" s="6" t="s">
@@ -16269,27 +16271,27 @@
         <v>55</v>
       </c>
     </row>
-    <row r="451" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A451" s="12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B451" s="13" t="s">
         <v>27</v>
       </c>
       <c r="C451" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D451" s="14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E451" s="14"/>
       <c r="F451" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G451" s="14"/>
       <c r="H451" s="14"/>
       <c r="I451" s="14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J451" s="14"/>
       <c r="K451" s="14" t="s">
@@ -16299,9 +16301,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="452" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A452" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B452" s="5" t="s">
         <v>13</v>
@@ -16310,15 +16312,15 @@
         <v>84</v>
       </c>
       <c r="D452" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E452" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F452" s="7"/>
       <c r="G452" s="7"/>
       <c r="H452" s="7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I452" s="7"/>
       <c r="J452" s="7" t="s">
@@ -16331,9 +16333,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="453" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A453" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B453" s="10" t="s">
         <v>16</v>
@@ -16342,13 +16344,13 @@
         <v>89</v>
       </c>
       <c r="D453" s="6" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E453" s="6"/>
       <c r="F453" s="6"/>
       <c r="G453" s="6"/>
       <c r="H453" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I453" s="6"/>
       <c r="J453" s="6" t="s">
@@ -16361,24 +16363,24 @@
         <v>119</v>
       </c>
     </row>
-    <row r="454" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A454" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B454" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C454" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D454" s="6"/>
       <c r="E454" s="6" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F454" s="6"/>
       <c r="G454" s="6"/>
       <c r="H454" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I454" s="6"/>
       <c r="J454" s="6" t="s">
@@ -16391,26 +16393,26 @@
         <v>119</v>
       </c>
     </row>
-    <row r="455" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A455" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B455" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C455" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D455" s="6" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E455" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F455" s="6"/>
       <c r="G455" s="6"/>
       <c r="H455" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I455" s="6"/>
       <c r="J455" s="6" t="s">
@@ -16423,9 +16425,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="456" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A456" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B456" s="10" t="s">
         <v>25</v>
@@ -16435,12 +16437,12 @@
       </c>
       <c r="D456" s="6"/>
       <c r="E456" s="6" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F456" s="6"/>
       <c r="G456" s="6"/>
       <c r="H456" s="6" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I456" s="6"/>
       <c r="J456" s="6" t="s">
@@ -16453,9 +16455,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="457" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A457" s="12" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B457" s="13" t="s">
         <v>27</v>
@@ -16464,15 +16466,15 @@
         <v>397</v>
       </c>
       <c r="D457" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E457" s="14"/>
       <c r="F457" s="14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G457" s="14"/>
       <c r="H457" s="14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="I457" s="14"/>
       <c r="J457" s="14" t="s">
@@ -16485,9 +16487,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="458" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A458" s="12" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B458" s="5" t="s">
         <v>13</v>
@@ -16495,7 +16497,7 @@
       <c r="C458" s="6"/>
       <c r="D458" s="7"/>
       <c r="E458" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F458" s="7"/>
       <c r="G458" s="7"/>
@@ -16505,9 +16507,9 @@
       <c r="K458" s="7"/>
       <c r="L458" s="8"/>
     </row>
-    <row r="459" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A459" s="12" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B459" s="10" t="s">
         <v>16</v>
@@ -16515,7 +16517,7 @@
       <c r="C459" s="6"/>
       <c r="D459" s="6"/>
       <c r="E459" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F459" s="6"/>
       <c r="G459" s="6"/>
@@ -16525,9 +16527,9 @@
       <c r="K459" s="6"/>
       <c r="L459" s="11"/>
     </row>
-    <row r="460" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A460" s="12" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B460" s="10" t="s">
         <v>20</v>
@@ -16535,10 +16537,10 @@
       <c r="C460" s="6"/>
       <c r="D460" s="6"/>
       <c r="E460" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F460" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G460" s="6"/>
       <c r="H460" s="6"/>
@@ -16547,9 +16549,9 @@
       <c r="K460" s="6"/>
       <c r="L460" s="11"/>
     </row>
-    <row r="461" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A461" s="12" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B461" s="10" t="s">
         <v>22</v>
@@ -16557,10 +16559,10 @@
       <c r="C461" s="6"/>
       <c r="D461" s="6"/>
       <c r="E461" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F461" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G461" s="6"/>
       <c r="H461" s="6"/>
@@ -16569,9 +16571,9 @@
       <c r="K461" s="6"/>
       <c r="L461" s="11"/>
     </row>
-    <row r="462" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A462" s="12" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B462" s="10" t="s">
         <v>25</v>
@@ -16580,7 +16582,7 @@
       <c r="D462" s="6"/>
       <c r="E462" s="6"/>
       <c r="F462" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G462" s="6"/>
       <c r="H462" s="6"/>
@@ -16589,9 +16591,9 @@
       <c r="K462" s="6"/>
       <c r="L462" s="11"/>
     </row>
-    <row r="463" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A463" s="12" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B463" s="13" t="s">
         <v>27</v>
@@ -16600,7 +16602,7 @@
       <c r="D463" s="14"/>
       <c r="E463" s="14"/>
       <c r="F463" s="14" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G463" s="14"/>
       <c r="H463" s="14"/>
@@ -16609,9 +16611,9 @@
       <c r="K463" s="14"/>
       <c r="L463" s="15"/>
     </row>
-    <row r="464" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A464" s="12" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B464" s="5" t="s">
         <v>13</v>
@@ -16619,7 +16621,7 @@
       <c r="C464" s="6"/>
       <c r="D464" s="7"/>
       <c r="E464" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F464" s="7" t="s">
         <v>239</v>
@@ -16629,19 +16631,19 @@
       </c>
       <c r="H464" s="7"/>
       <c r="I464" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J464" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K464" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L464" s="8"/>
     </row>
-    <row r="465" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A465" s="12" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B465" s="10" t="s">
         <v>16</v>
@@ -16649,7 +16651,7 @@
       <c r="C465" s="6"/>
       <c r="D465" s="6"/>
       <c r="E465" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F465" s="6" t="s">
         <v>239</v>
@@ -16659,17 +16661,17 @@
       </c>
       <c r="H465" s="6"/>
       <c r="I465" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J465" s="6"/>
       <c r="K465" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L465" s="11"/>
     </row>
-    <row r="466" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A466" s="12" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B466" s="10" t="s">
         <v>20</v>
@@ -16677,7 +16679,7 @@
       <c r="C466" s="6"/>
       <c r="D466" s="6"/>
       <c r="E466" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F466" s="6" t="s">
         <v>131</v>
@@ -16687,17 +16689,17 @@
       </c>
       <c r="H466" s="6"/>
       <c r="I466" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J466" s="6"/>
       <c r="K466" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L466" s="11"/>
     </row>
-    <row r="467" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A467" s="12" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B467" s="10" t="s">
         <v>22</v>
@@ -16705,7 +16707,7 @@
       <c r="C467" s="6"/>
       <c r="D467" s="6"/>
       <c r="E467" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F467" s="6" t="s">
         <v>131</v>
@@ -16717,13 +16719,13 @@
       <c r="I467" s="6"/>
       <c r="J467" s="6"/>
       <c r="K467" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L467" s="11"/>
     </row>
-    <row r="468" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A468" s="12" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B468" s="10" t="s">
         <v>25</v>
@@ -16731,7 +16733,7 @@
       <c r="C468" s="6"/>
       <c r="D468" s="6"/>
       <c r="E468" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F468" s="6" t="s">
         <v>131</v>
@@ -16749,9 +16751,9 @@
       <c r="K468" s="6"/>
       <c r="L468" s="11"/>
     </row>
-    <row r="469" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A469" s="12" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B469" s="13" t="s">
         <v>27</v>
@@ -16759,7 +16761,7 @@
       <c r="C469" s="14"/>
       <c r="D469" s="14"/>
       <c r="E469" s="14" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F469" s="14" t="s">
         <v>131</v>
@@ -16769,17 +16771,17 @@
       </c>
       <c r="H469" s="14"/>
       <c r="I469" s="14" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J469" s="14" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K469" s="14"/>
       <c r="L469" s="15"/>
     </row>
-    <row r="470" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A470" s="12" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B470" s="5" t="s">
         <v>13</v>
@@ -16787,16 +16789,16 @@
       <c r="C470" s="6"/>
       <c r="D470" s="7"/>
       <c r="E470" s="7" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F470" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G470" s="7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H470" s="7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I470" s="7"/>
       <c r="J470" s="7" t="s">
@@ -16807,9 +16809,9 @@
       </c>
       <c r="L470" s="8"/>
     </row>
-    <row r="471" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A471" s="12" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B471" s="10" t="s">
         <v>16</v>
@@ -16818,14 +16820,14 @@
       <c r="D471" s="6"/>
       <c r="E471" s="6"/>
       <c r="F471" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G471" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H471" s="6"/>
       <c r="I471" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J471" s="6" t="s">
         <v>393</v>
@@ -16835,9 +16837,9 @@
       </c>
       <c r="L471" s="11"/>
     </row>
-    <row r="472" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A472" s="12" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B472" s="10" t="s">
         <v>20</v>
@@ -16847,16 +16849,16 @@
       </c>
       <c r="D472" s="6"/>
       <c r="E472" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F472" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G472" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H472" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I472" s="6"/>
       <c r="J472" s="6" t="s">
@@ -16867,9 +16869,9 @@
       </c>
       <c r="L472" s="11"/>
     </row>
-    <row r="473" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A473" s="12" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B473" s="10" t="s">
         <v>22</v>
@@ -16879,17 +16881,17 @@
       </c>
       <c r="D473" s="6"/>
       <c r="E473" s="6" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F473" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G473" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H473" s="6"/>
       <c r="I473" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J473" s="6" t="s">
         <v>393</v>
@@ -16899,9 +16901,9 @@
       </c>
       <c r="L473" s="11"/>
     </row>
-    <row r="474" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A474" s="12" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B474" s="10" t="s">
         <v>25</v>
@@ -16911,13 +16913,13 @@
       </c>
       <c r="D474" s="6"/>
       <c r="E474" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F474" s="6"/>
       <c r="G474" s="6"/>
       <c r="H474" s="6"/>
       <c r="I474" s="6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J474" s="6" t="s">
         <v>393</v>
@@ -16927,9 +16929,9 @@
       </c>
       <c r="L474" s="11"/>
     </row>
-    <row r="475" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A475" s="12" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B475" s="13" t="s">
         <v>27</v>
@@ -16939,15 +16941,15 @@
       </c>
       <c r="D475" s="14"/>
       <c r="E475" s="14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F475" s="14" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G475" s="14"/>
       <c r="H475" s="14"/>
       <c r="I475" s="14" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J475" s="14" t="s">
         <v>393</v>
@@ -16957,85 +16959,97 @@
       </c>
       <c r="L475" s="15"/>
     </row>
-    <row r="476" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A476" s="12" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B476" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C476" s="6"/>
-      <c r="D476" s="7"/>
+      <c r="D476" s="7" t="s">
+        <v>520</v>
+      </c>
       <c r="E476" s="7" t="s">
         <v>399</v>
       </c>
       <c r="F476" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G476" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="H476" s="7"/>
+        <v>488</v>
+      </c>
+      <c r="H476" s="7" t="s">
+        <v>506</v>
+      </c>
       <c r="I476" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J476" s="7"/>
       <c r="K476" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L476" s="8"/>
     </row>
-    <row r="477" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A477" s="12" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B477" s="10" t="s">
         <v>16</v>
       </c>
       <c r="C477" s="6"/>
-      <c r="D477" s="6"/>
+      <c r="D477" s="6" t="s">
+        <v>521</v>
+      </c>
       <c r="E477" s="6" t="s">
         <v>399</v>
       </c>
       <c r="F477" s="6"/>
       <c r="G477" s="6" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H477" s="6"/>
       <c r="I477" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J477" s="6"/>
       <c r="K477" s="6" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L477" s="11"/>
     </row>
-    <row r="478" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A478" s="12" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B478" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C478" s="6"/>
-      <c r="D478" s="6"/>
+      <c r="D478" s="6" t="s">
+        <v>521</v>
+      </c>
       <c r="E478" s="6" t="s">
         <v>399</v>
       </c>
       <c r="F478" s="6"/>
       <c r="G478" s="6"/>
-      <c r="H478" s="6"/>
+      <c r="H478" s="6" t="s">
+        <v>489</v>
+      </c>
       <c r="I478" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="J478" s="6"/>
+        <v>506</v>
+      </c>
+      <c r="J478" s="6" t="s">
+        <v>520</v>
+      </c>
       <c r="K478" s="6"/>
       <c r="L478" s="11"/>
     </row>
-    <row r="479" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A479" s="12" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B479" s="10" t="s">
         <v>22</v>
@@ -17043,47 +17057,59 @@
       <c r="C479" s="6"/>
       <c r="D479" s="6"/>
       <c r="E479" s="6" t="s">
-        <v>490</v>
-      </c>
-      <c r="F479" s="6"/>
+        <v>491</v>
+      </c>
+      <c r="F479" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="G479" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H479" s="6"/>
-      <c r="I479" s="6"/>
-      <c r="J479" s="6"/>
+      <c r="I479" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="J479" s="6" t="s">
+        <v>520</v>
+      </c>
       <c r="K479" s="6"/>
       <c r="L479" s="11"/>
     </row>
-    <row r="480" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A480" s="12" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B480" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C480" s="6"/>
-      <c r="D480" s="6"/>
+      <c r="D480" s="6" t="s">
+        <v>521</v>
+      </c>
       <c r="E480" s="6" t="s">
-        <v>490</v>
-      </c>
-      <c r="F480" s="6"/>
+        <v>491</v>
+      </c>
+      <c r="F480" s="6" t="s">
+        <v>520</v>
+      </c>
       <c r="G480" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="H480" s="6"/>
+        <v>488</v>
+      </c>
+      <c r="H480" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="I480" s="6"/>
       <c r="J480" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="K480" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="K480" s="6" t="s">
-        <v>491</v>
-      </c>
       <c r="L480" s="11"/>
     </row>
-    <row r="481" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A481" s="12" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B481" s="13" t="s">
         <v>27</v>
@@ -17091,23 +17117,23 @@
       <c r="C481" s="14"/>
       <c r="D481" s="14"/>
       <c r="E481" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F481" s="14" t="s">
         <v>490</v>
-      </c>
-      <c r="F481" s="14" t="s">
-        <v>489</v>
       </c>
       <c r="G481" s="14"/>
       <c r="H481" s="14"/>
       <c r="I481" s="14"/>
       <c r="J481" s="14"/>
       <c r="K481" s="14" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L481" s="15"/>
     </row>
-    <row r="482" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A482" s="12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B482" s="5" t="s">
         <v>13</v>
@@ -17115,27 +17141,27 @@
       <c r="C482" s="6"/>
       <c r="D482" s="7"/>
       <c r="E482" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F482" s="7" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G482" s="7" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H482" s="7"/>
       <c r="I482" s="7"/>
       <c r="J482" s="7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K482" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L482" s="8"/>
     </row>
-    <row r="483" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A483" s="12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B483" s="10" t="s">
         <v>16</v>
@@ -17143,23 +17169,23 @@
       <c r="C483" s="6"/>
       <c r="D483" s="6"/>
       <c r="E483" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F483" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G483" s="6"/>
       <c r="H483" s="6"/>
       <c r="I483" s="6"/>
       <c r="J483" s="6"/>
       <c r="K483" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L483" s="11"/>
     </row>
-    <row r="484" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A484" s="12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B484" s="10" t="s">
         <v>20</v>
@@ -17167,23 +17193,23 @@
       <c r="C484" s="6"/>
       <c r="D484" s="6"/>
       <c r="E484" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F484" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G484" s="6"/>
       <c r="H484" s="6"/>
       <c r="I484" s="6" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J484" s="6"/>
       <c r="K484" s="6"/>
       <c r="L484" s="11"/>
     </row>
-    <row r="485" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A485" s="12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B485" s="10" t="s">
         <v>22</v>
@@ -17201,9 +17227,9 @@
       <c r="K485" s="6"/>
       <c r="L485" s="11"/>
     </row>
-    <row r="486" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A486" s="12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B486" s="10" t="s">
         <v>25</v>
@@ -17212,10 +17238,10 @@
       <c r="D486" s="6"/>
       <c r="E486" s="6"/>
       <c r="F486" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G486" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H486" s="6"/>
       <c r="I486" s="6" t="s">
@@ -17223,13 +17249,13 @@
       </c>
       <c r="J486" s="6"/>
       <c r="K486" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L486" s="11"/>
     </row>
-    <row r="487" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A487" s="12" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B487" s="13" t="s">
         <v>27</v>
@@ -17238,10 +17264,10 @@
       <c r="D487" s="14"/>
       <c r="E487" s="14"/>
       <c r="F487" s="14" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G487" s="14" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H487" s="14"/>
       <c r="I487" s="14" t="s">
@@ -17251,9 +17277,9 @@
       <c r="K487" s="14"/>
       <c r="L487" s="15"/>
     </row>
-    <row r="488" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A488" s="12" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B488" s="5" t="s">
         <v>13</v>
@@ -17271,13 +17297,13 @@
       </c>
       <c r="J488" s="7"/>
       <c r="K488" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="L488" s="8"/>
+    </row>
+    <row r="489" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A489" s="12" t="s">
         <v>503</v>
-      </c>
-      <c r="L488" s="8"/>
-    </row>
-    <row r="489" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A489" s="12" t="s">
-        <v>502</v>
       </c>
       <c r="B489" s="10" t="s">
         <v>16</v>
@@ -17303,13 +17329,13 @@
       </c>
       <c r="J489" s="6"/>
       <c r="K489" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="L489" s="11"/>
+    </row>
+    <row r="490" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A490" s="12" t="s">
         <v>503</v>
-      </c>
-      <c r="L489" s="11"/>
-    </row>
-    <row r="490" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A490" s="12" t="s">
-        <v>502</v>
       </c>
       <c r="B490" s="10" t="s">
         <v>20</v>
@@ -17333,13 +17359,13 @@
         <v>113</v>
       </c>
       <c r="K490" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="L490" s="11"/>
+    </row>
+    <row r="491" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A491" s="12" t="s">
         <v>503</v>
-      </c>
-      <c r="L490" s="11"/>
-    </row>
-    <row r="491" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A491" s="12" t="s">
-        <v>502</v>
       </c>
       <c r="B491" s="10" t="s">
         <v>22</v>
@@ -17347,7 +17373,7 @@
       <c r="C491" s="6"/>
       <c r="D491" s="6"/>
       <c r="E491" s="6" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F491" s="6"/>
       <c r="G491" s="6" t="s">
@@ -17361,13 +17387,13 @@
       </c>
       <c r="J491" s="6"/>
       <c r="K491" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="L491" s="11"/>
+    </row>
+    <row r="492" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A492" s="12" t="s">
         <v>503</v>
-      </c>
-      <c r="L491" s="11"/>
-    </row>
-    <row r="492" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A492" s="12" t="s">
-        <v>502</v>
       </c>
       <c r="B492" s="10" t="s">
         <v>25</v>
@@ -17375,7 +17401,7 @@
       <c r="C492" s="6"/>
       <c r="D492" s="6"/>
       <c r="E492" s="6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F492" s="6" t="s">
         <v>128</v>
@@ -17389,13 +17415,13 @@
       <c r="I492" s="6"/>
       <c r="J492" s="6"/>
       <c r="K492" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="L492" s="11"/>
+    </row>
+    <row r="493" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A493" s="12" t="s">
         <v>503</v>
-      </c>
-      <c r="L492" s="11"/>
-    </row>
-    <row r="493" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A493" s="12" t="s">
-        <v>502</v>
       </c>
       <c r="B493" s="13" t="s">
         <v>27</v>
@@ -17417,9 +17443,9 @@
       <c r="K493" s="14"/>
       <c r="L493" s="15"/>
     </row>
-    <row r="494" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A494" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B494" s="5" t="s">
         <v>13</v>
@@ -17445,9 +17471,9 @@
       </c>
       <c r="L494" s="8"/>
     </row>
-    <row r="495" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A495" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B495" s="10" t="s">
         <v>16</v>
@@ -17471,9 +17497,9 @@
       </c>
       <c r="L495" s="11"/>
     </row>
-    <row r="496" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A496" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B496" s="10" t="s">
         <v>20</v>
@@ -17495,13 +17521,13 @@
         <v>99</v>
       </c>
       <c r="K496" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L496" s="11"/>
     </row>
-    <row r="497" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A497" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B497" s="10" t="s">
         <v>22</v>
@@ -17523,13 +17549,13 @@
         <v>97</v>
       </c>
       <c r="K497" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L497" s="11"/>
     </row>
-    <row r="498" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A498" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B498" s="10" t="s">
         <v>25</v>
@@ -17549,13 +17575,13 @@
       </c>
       <c r="J498" s="6"/>
       <c r="K498" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L498" s="11"/>
     </row>
-    <row r="499" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A499" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B499" s="13" t="s">
         <v>27</v>
@@ -17579,9 +17605,9 @@
       </c>
       <c r="L499" s="15"/>
     </row>
-    <row r="500" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A500" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B500" s="5" t="s">
         <v>13</v>
@@ -17603,13 +17629,13 @@
         <v>121</v>
       </c>
       <c r="K500" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L500" s="8"/>
     </row>
-    <row r="501" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A501" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B501" s="10" t="s">
         <v>16</v>
@@ -17631,13 +17657,13 @@
       </c>
       <c r="J501" s="6"/>
       <c r="K501" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L501" s="11"/>
     </row>
-    <row r="502" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A502" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B502" s="10" t="s">
         <v>20</v>
@@ -17659,13 +17685,13 @@
       <c r="I502" s="6"/>
       <c r="J502" s="6"/>
       <c r="K502" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L502" s="11"/>
     </row>
-    <row r="503" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A503" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B503" s="10" t="s">
         <v>22</v>
@@ -17689,13 +17715,13 @@
         <v>128</v>
       </c>
       <c r="K503" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L503" s="11"/>
     </row>
-    <row r="504" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A504" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B504" s="10" t="s">
         <v>25</v>
@@ -17715,13 +17741,13 @@
         <v>88</v>
       </c>
       <c r="K504" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L504" s="11"/>
     </row>
-    <row r="505" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A505" s="12" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B505" s="13" t="s">
         <v>27</v>
@@ -17743,9 +17769,9 @@
       <c r="K505" s="14"/>
       <c r="L505" s="15"/>
     </row>
-    <row r="506" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A506" s="12" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B506" s="5" t="s">
         <v>13</v>
@@ -17753,10 +17779,10 @@
       <c r="C506" s="6"/>
       <c r="D506" s="7"/>
       <c r="E506" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F506" s="7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G506" s="7" t="s">
         <v>104</v>
@@ -17766,14 +17792,14 @@
       </c>
       <c r="I506" s="7"/>
       <c r="J506" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K506" s="7"/>
       <c r="L506" s="8"/>
     </row>
-    <row r="507" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A507" s="12" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B507" s="10" t="s">
         <v>16</v>
@@ -17781,40 +17807,38 @@
       <c r="C507" s="6"/>
       <c r="D507" s="6"/>
       <c r="E507" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F507" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="G507" s="6" t="s">
         <v>82</v>
       </c>
+      <c r="G507" s="6"/>
       <c r="H507" s="6" t="s">
         <v>114</v>
       </c>
       <c r="I507" s="6"/>
       <c r="J507" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K507" s="6"/>
       <c r="L507" s="11"/>
     </row>
-    <row r="508" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A508" s="12" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B508" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C508" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D508" s="6"/>
       <c r="E508" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F508" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G508" s="6"/>
       <c r="H508" s="6" t="s">
@@ -17822,27 +17846,27 @@
       </c>
       <c r="I508" s="6"/>
       <c r="J508" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K508" s="6"/>
       <c r="L508" s="11"/>
     </row>
-    <row r="509" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A509" s="12" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B509" s="10" t="s">
         <v>22</v>
       </c>
       <c r="C509" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D509" s="6"/>
       <c r="E509" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F509" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G509" s="6" t="s">
         <v>120</v>
@@ -17852,14 +17876,14 @@
       </c>
       <c r="I509" s="6"/>
       <c r="J509" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K509" s="6"/>
       <c r="L509" s="11"/>
     </row>
-    <row r="510" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A510" s="12" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B510" s="10" t="s">
         <v>25</v>
@@ -17870,7 +17894,7 @@
         <v>511</v>
       </c>
       <c r="F510" s="6" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G510" s="6" t="s">
         <v>119</v>
@@ -17880,14 +17904,14 @@
       </c>
       <c r="I510" s="6"/>
       <c r="J510" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K510" s="6"/>
       <c r="L510" s="11"/>
     </row>
-    <row r="511" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A511" s="12" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B511" s="13" t="s">
         <v>27</v>
@@ -17898,7 +17922,7 @@
         <v>512</v>
       </c>
       <c r="F511" s="14" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G511" s="14" t="s">
         <v>127</v>
@@ -17908,12 +17932,12 @@
       </c>
       <c r="I511" s="14"/>
       <c r="J511" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K511" s="14"/>
       <c r="L511" s="15"/>
     </row>
-    <row r="512" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A512" s="12" t="s">
         <v>513</v>
       </c>
@@ -17928,7 +17952,7 @@
         <v>514</v>
       </c>
       <c r="F512" s="7" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G512" s="7"/>
       <c r="H512" s="7"/>
@@ -17937,11 +17961,11 @@
       </c>
       <c r="J512" s="7"/>
       <c r="K512" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L512" s="8"/>
     </row>
-    <row r="513" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A513" s="12" t="s">
         <v>513</v>
       </c>
@@ -17956,7 +17980,7 @@
         <v>516</v>
       </c>
       <c r="F513" s="6" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G513" s="6"/>
       <c r="H513" s="6"/>
@@ -17965,11 +17989,11 @@
         <v>417</v>
       </c>
       <c r="K513" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L513" s="11"/>
     </row>
-    <row r="514" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A514" s="12" t="s">
         <v>513</v>
       </c>
@@ -17995,11 +18019,11 @@
       </c>
       <c r="J514" s="6"/>
       <c r="K514" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L514" s="11"/>
     </row>
-    <row r="515" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A515" s="12" t="s">
         <v>513</v>
       </c>
@@ -18025,11 +18049,11 @@
         <v>522</v>
       </c>
       <c r="K515" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L515" s="11"/>
     </row>
-    <row r="516" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A516" s="12" t="s">
         <v>513</v>
       </c>
@@ -18053,11 +18077,11 @@
         <v>115</v>
       </c>
       <c r="K516" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L516" s="11"/>
     </row>
-    <row r="517" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A517" s="12" t="s">
         <v>513</v>
       </c>
@@ -18075,7 +18099,7 @@
       <c r="K517" s="14"/>
       <c r="L517" s="15"/>
     </row>
-    <row r="518" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A518" s="12" t="s">
         <v>523</v>
       </c>
@@ -18099,11 +18123,11 @@
       <c r="I518" s="7"/>
       <c r="J518" s="7"/>
       <c r="K518" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L518" s="8"/>
     </row>
-    <row r="519" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A519" s="12" t="s">
         <v>523</v>
       </c>
@@ -18127,11 +18151,11 @@
         <v>525</v>
       </c>
       <c r="K519" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L519" s="11"/>
     </row>
-    <row r="520" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A520" s="12" t="s">
         <v>523</v>
       </c>
@@ -18155,11 +18179,11 @@
         <v>96</v>
       </c>
       <c r="K520" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L520" s="11"/>
     </row>
-    <row r="521" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A521" s="12" t="s">
         <v>523</v>
       </c>
@@ -18185,11 +18209,11 @@
         <v>420</v>
       </c>
       <c r="K521" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L521" s="11"/>
     </row>
-    <row r="522" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A522" s="12" t="s">
         <v>523</v>
       </c>
@@ -18213,11 +18237,11 @@
       </c>
       <c r="J522" s="6"/>
       <c r="K522" s="6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L522" s="11"/>
     </row>
-    <row r="523" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A523" s="12" t="s">
         <v>523</v>
       </c>
@@ -18241,7 +18265,7 @@
       <c r="K523" s="14"/>
       <c r="L523" s="15"/>
     </row>
-    <row r="524" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A524" s="22" t="s">
         <v>529</v>
       </c>
@@ -18271,7 +18295,7 @@
       </c>
       <c r="L524" s="8"/>
     </row>
-    <row r="525" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A525" s="22" t="s">
         <v>529</v>
       </c>
@@ -18299,7 +18323,7 @@
       </c>
       <c r="L525" s="11"/>
     </row>
-    <row r="526" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A526" s="22" t="s">
         <v>529</v>
       </c>
@@ -18327,7 +18351,7 @@
       </c>
       <c r="L526" s="11"/>
     </row>
-    <row r="527" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A527" s="22" t="s">
         <v>529</v>
       </c>
@@ -18355,7 +18379,7 @@
       <c r="K527" s="6"/>
       <c r="L527" s="11"/>
     </row>
-    <row r="528" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A528" s="22" t="s">
         <v>529</v>
       </c>
@@ -18385,7 +18409,7 @@
       </c>
       <c r="L528" s="11"/>
     </row>
-    <row r="529" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A529" s="22" t="s">
         <v>529</v>
       </c>
@@ -18415,7 +18439,7 @@
       </c>
       <c r="L529" s="23"/>
     </row>
-    <row r="530" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A530" s="12" t="s">
         <v>530</v>
       </c>
@@ -18443,7 +18467,7 @@
       <c r="K530" s="5"/>
       <c r="L530" s="24"/>
     </row>
-    <row r="531" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A531" s="12" t="s">
         <v>530</v>
       </c>
@@ -18471,7 +18495,7 @@
       </c>
       <c r="L531" s="25"/>
     </row>
-    <row r="532" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A532" s="12" t="s">
         <v>530</v>
       </c>
@@ -18499,7 +18523,7 @@
       </c>
       <c r="L532" s="25"/>
     </row>
-    <row r="533" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A533" s="12" t="s">
         <v>530</v>
       </c>
@@ -18529,7 +18553,7 @@
       </c>
       <c r="L533" s="25"/>
     </row>
-    <row r="534" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A534" s="12" t="s">
         <v>530</v>
       </c>
@@ -18557,7 +18581,7 @@
       <c r="K534" s="10"/>
       <c r="L534" s="25"/>
     </row>
-    <row r="535" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A535" s="12" t="s">
         <v>530</v>
       </c>
@@ -18566,23 +18590,23 @@
       </c>
       <c r="C535" s="13"/>
       <c r="D535" s="13"/>
-      <c r="E535" s="27" t="s">
+      <c r="E535" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="F535" s="27" t="s">
+      <c r="F535" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="G535" s="27" t="s">
+      <c r="G535" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="H535" s="27" t="s">
+      <c r="H535" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="I535" s="27" t="s">
+      <c r="I535" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="J535" s="27"/>
-      <c r="K535" s="27" t="s">
+      <c r="J535" s="13"/>
+      <c r="K535" s="13" t="s">
         <v>99</v>
       </c>
       <c r="L535" s="26"/>
